--- a/Fit Results/Together.xlsx
+++ b/Fit Results/Together.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Diego\git\6s7p\Fit Results\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wolfw\git\6s7p\Fit Results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{724D6A98-F0F0-4AA0-9457-9FDD1BE97A79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B348D4B-29EE-4B77-B19F-732B18DC32D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="19392" windowHeight="10992" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="F1=3" sheetId="1" r:id="rId1"/>
@@ -32,15 +32,12 @@
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="387" uniqueCount="384">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="441" uniqueCount="418">
   <si>
     <t>Date</t>
   </si>
@@ -1192,6 +1189,108 @@
   </si>
   <si>
     <t>F1=4</t>
+  </si>
+  <si>
+    <t>g1</t>
+  </si>
+  <si>
+    <t>g2</t>
+  </si>
+  <si>
+    <t>g3</t>
+  </si>
+  <si>
+    <t>Jul06,2026+1-29-35PM</t>
+  </si>
+  <si>
+    <t>Jul06,2026+1-39-06PM</t>
+  </si>
+  <si>
+    <t>Jul06,2026+1-47-03PM</t>
+  </si>
+  <si>
+    <t>Jul06,2026+1-55-02PM</t>
+  </si>
+  <si>
+    <t>Jul06,2026+2-03-11PM</t>
+  </si>
+  <si>
+    <t>Jul06,2026+2-11-08PM</t>
+  </si>
+  <si>
+    <t>Jul06,2026+2-19-07PM</t>
+  </si>
+  <si>
+    <t>Jul06,2026+2-27-28PM</t>
+  </si>
+  <si>
+    <t>Jul06,2026+2-35-31PM</t>
+  </si>
+  <si>
+    <t>Jul06,2026+2-43-35PM</t>
+  </si>
+  <si>
+    <t>Jul06,2026+2-52-04PM</t>
+  </si>
+  <si>
+    <t>Jul06,2026+3-00-09PM</t>
+  </si>
+  <si>
+    <t>Jul06,2026+3-08-06PM</t>
+  </si>
+  <si>
+    <t>Jul06,2026+3-16-13PM</t>
+  </si>
+  <si>
+    <t>Jul06,2026+3-24-12PM</t>
+  </si>
+  <si>
+    <t>Jul06,2026+3-32-14PM</t>
+  </si>
+  <si>
+    <t>Jul06,2026+3-40-12PM</t>
+  </si>
+  <si>
+    <t>Jul06,2026+3-49-10PM</t>
+  </si>
+  <si>
+    <t>Jul06,2026+3-57-16PM</t>
+  </si>
+  <si>
+    <t>Jul06,2026+4-06-07PM</t>
+  </si>
+  <si>
+    <t>Jul06,2026+4-14-01PM</t>
+  </si>
+  <si>
+    <t>Jul06,2026+4-21-57PM</t>
+  </si>
+  <si>
+    <t>Jul06,2026+4-29-54PM</t>
+  </si>
+  <si>
+    <t>Jul06,2026+4-37-56PM</t>
+  </si>
+  <si>
+    <t>Jul06,2026+4-47-16PM</t>
+  </si>
+  <si>
+    <t>Jul06,2026+4-56-24PM</t>
+  </si>
+  <si>
+    <t>Jul06,2026+5-05-27PM</t>
+  </si>
+  <si>
+    <t>Jul06,2026+5-13-36PM</t>
+  </si>
+  <si>
+    <t>Jul06,2026+5-21-38PM</t>
+  </si>
+  <si>
+    <t>Jul06,2026+5-31-27PM</t>
+  </si>
+  <si>
+    <t>Jul06,2026+5-39-26PM</t>
   </si>
 </sst>
 </file>
@@ -2137,6 +2236,24 @@
                 <c:pt idx="257">
                   <c:v>14.491750683935599</c:v>
                 </c:pt>
+                <c:pt idx="258">
+                  <c:v>17.825013007136501</c:v>
+                </c:pt>
+                <c:pt idx="259">
+                  <c:v>17.9319730766783</c:v>
+                </c:pt>
+                <c:pt idx="260">
+                  <c:v>18.039044650769</c:v>
+                </c:pt>
+                <c:pt idx="261">
+                  <c:v>18.0604756933053</c:v>
+                </c:pt>
+                <c:pt idx="262">
+                  <c:v>17.9979172106978</c:v>
+                </c:pt>
+                <c:pt idx="263">
+                  <c:v>17.998827423434999</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
@@ -2910,6 +3027,24 @@
                 </c:pt>
                 <c:pt idx="257">
                   <c:v>0.237718713583811</c:v>
+                </c:pt>
+                <c:pt idx="258">
+                  <c:v>0.29193451692567801</c:v>
+                </c:pt>
+                <c:pt idx="259">
+                  <c:v>0.28873287738484599</c:v>
+                </c:pt>
+                <c:pt idx="260">
+                  <c:v>0.28985427653153101</c:v>
+                </c:pt>
+                <c:pt idx="261">
+                  <c:v>0.29473582812057803</c:v>
+                </c:pt>
+                <c:pt idx="262">
+                  <c:v>0.29630016894823502</c:v>
+                </c:pt>
+                <c:pt idx="263">
+                  <c:v>0.290375757335809</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3066,6 +3201,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -3073,7 +3209,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -3109,6 +3244,343 @@
 </file>
 
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'F1=3'!$B$7:$B$26</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="20"/>
+                <c:pt idx="0">
+                  <c:v>8.53551089338964</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>8.2121360213246692</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>8.3727208112640206</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>8.4364141305933895</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>8.4084015562695207</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>8.5099572412062301</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>8.4321434520724008</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>8.4721216638779193</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>8.4953666075608503</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>8.7711252103094601</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>8.5801266895029205</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>8.5783681642005494</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>8.6129268121772302</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>8.6349505815443095</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>8.5827352500219707</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>8.6784045244654298</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>8.5889121451567796</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>8.2237273067390202</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>8.26640584418465</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>8.2614937671479094</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-370C-4803-9C29-64A60CA5C3C8}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="568739376"/>
+        <c:axId val="568739728"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="568739376"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="568739728"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="568739728"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="568739376"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -4108,6 +4580,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -4115,7 +4588,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -4150,7 +4622,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -6523,6 +6995,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -6530,7 +7003,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -6646,6 +7118,46 @@
 </file>
 
 <file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors4.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
   <a:schemeClr val="accent2"/>
@@ -8233,6 +8745,522 @@
 </cs:chartStyle>
 </file>
 
+<file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
@@ -8271,6 +9299,42 @@
     </xdr:graphicFrame>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>30480</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>445770</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>121920</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>445770</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Chart 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D520CA51-E76E-84A2-6718-39E3DE3537C2}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -8278,16 +9342,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>533400</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>128587</xdr:rowOff>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>274320</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>79057</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>18</xdr:col>
-      <xdr:colOff>228600</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>14287</xdr:rowOff>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>609600</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>513397</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -8619,10 +9683,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C265"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:H290"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <sheetData>
-    <row r="1" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -8633,7 +9697,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
@@ -8644,7 +9708,7 @@
         <v>0.14198189433295499</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
@@ -8655,7 +9719,7 @@
         <v>0.14200693706074399</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
@@ -8666,7 +9730,7 @@
         <v>0.13879302222888601</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="1" t="s">
         <v>6</v>
       </c>
@@ -8677,7 +9741,7 @@
         <v>0.14134057599559999</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="1" t="s">
         <v>7</v>
       </c>
@@ -8688,7 +9752,7 @@
         <v>0.14287369952523299</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="1" t="s">
         <v>8</v>
       </c>
@@ -8698,8 +9762,11 @@
       <c r="C7" s="1">
         <v>0.14242039757473199</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="G7" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="1" t="s">
         <v>9</v>
       </c>
@@ -8709,8 +9776,17 @@
       <c r="C8" s="1">
         <v>0.13513280226965799</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="F8" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="G8" s="1">
+        <v>8.2121360213246692</v>
+      </c>
+      <c r="H8" s="1">
+        <v>0.13513280226965799</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="1" t="s">
         <v>10</v>
       </c>
@@ -8720,8 +9796,17 @@
       <c r="C9" s="1">
         <v>0.13504563445130599</v>
       </c>
-    </row>
-    <row r="10" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="F9" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="G9" s="1">
+        <v>8.2237273067390202</v>
+      </c>
+      <c r="H9" s="1">
+        <v>0.136881983671574</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="1" t="s">
         <v>11</v>
       </c>
@@ -8731,8 +9816,17 @@
       <c r="C10" s="1">
         <v>0.13859780418944301</v>
       </c>
-    </row>
-    <row r="11" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="F10" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="G10" s="1">
+        <v>8.26640584418465</v>
+      </c>
+      <c r="H10" s="1">
+        <v>0.135891683439223</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="1" t="s">
         <v>12</v>
       </c>
@@ -8742,8 +9836,17 @@
       <c r="C11" s="1">
         <v>0.13768382280778599</v>
       </c>
-    </row>
-    <row r="12" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="F11" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G11" s="1">
+        <v>8.2614937671479094</v>
+      </c>
+      <c r="H11" s="1">
+        <v>0.134600217130598</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="1" t="s">
         <v>13</v>
       </c>
@@ -8753,8 +9856,11 @@
       <c r="C12" s="1">
         <v>0.137341027012235</v>
       </c>
-    </row>
-    <row r="13" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="G12" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="1" t="s">
         <v>14</v>
       </c>
@@ -8764,8 +9870,17 @@
       <c r="C13" s="1">
         <v>0.14146322755453</v>
       </c>
-    </row>
-    <row r="14" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="F13" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G13" s="1">
+        <v>8.3727208112640206</v>
+      </c>
+      <c r="H13" s="1">
+        <v>0.13504563445130599</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="1" t="s">
         <v>15</v>
       </c>
@@ -8775,8 +9890,17 @@
       <c r="C14" s="1">
         <v>0.1440878295095</v>
       </c>
-    </row>
-    <row r="15" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="F14" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G14" s="1">
+        <v>8.4364141305933895</v>
+      </c>
+      <c r="H14" s="1">
+        <v>0.13859780418944301</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="1" t="s">
         <v>16</v>
       </c>
@@ -8786,8 +9910,17 @@
       <c r="C15" s="1">
         <v>0.139203017324112</v>
       </c>
-    </row>
-    <row r="16" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="F15" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G15" s="1">
+        <v>8.4084015562695207</v>
+      </c>
+      <c r="H15" s="1">
+        <v>0.13768382280778599</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="1" t="s">
         <v>17</v>
       </c>
@@ -8797,8 +9930,17 @@
       <c r="C16" s="1">
         <v>0.14444988833485001</v>
       </c>
-    </row>
-    <row r="17" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="F16" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G16" s="1">
+        <v>8.5099572412062301</v>
+      </c>
+      <c r="H16" s="1">
+        <v>0.137341027012235</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="1" t="s">
         <v>18</v>
       </c>
@@ -8808,8 +9950,17 @@
       <c r="C17" s="1">
         <v>0.14486186097849299</v>
       </c>
-    </row>
-    <row r="18" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="F17" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G17" s="1">
+        <v>8.4321434520724008</v>
+      </c>
+      <c r="H17" s="1">
+        <v>0.14146322755453</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="1" t="s">
         <v>19</v>
       </c>
@@ -8819,8 +9970,17 @@
       <c r="C18" s="1">
         <v>0.14493175120103199</v>
       </c>
-    </row>
-    <row r="19" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="F18" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G18" s="1">
+        <v>8.4721216638779193</v>
+      </c>
+      <c r="H18" s="1">
+        <v>0.1440878295095</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="1" t="s">
         <v>20</v>
       </c>
@@ -8830,8 +9990,17 @@
       <c r="C19" s="1">
         <v>0.14335784354365599</v>
       </c>
-    </row>
-    <row r="20" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="F19" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G19" s="1">
+        <v>8.4953666075608503</v>
+      </c>
+      <c r="H19" s="1">
+        <v>0.139203017324112</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="1" t="s">
         <v>21</v>
       </c>
@@ -8841,8 +10010,11 @@
       <c r="C20" s="1">
         <v>0.14372426788936199</v>
       </c>
-    </row>
-    <row r="21" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="G20" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" s="1" t="s">
         <v>22</v>
       </c>
@@ -8852,8 +10024,17 @@
       <c r="C21" s="1">
         <v>0.140914458888726</v>
       </c>
-    </row>
-    <row r="22" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="F21" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G21" s="1">
+        <v>8.53551089338964</v>
+      </c>
+      <c r="H21" s="1">
+        <v>0.14242039757473199</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="1" t="s">
         <v>23</v>
       </c>
@@ -8863,8 +10044,17 @@
       <c r="C22" s="1">
         <v>0.144559929539015</v>
       </c>
-    </row>
-    <row r="23" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="F22" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G22" s="1">
+        <v>8.7711252103094601</v>
+      </c>
+      <c r="H22" s="1">
+        <v>0.14444988833485001</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" s="1" t="s">
         <v>24</v>
       </c>
@@ -8874,8 +10064,17 @@
       <c r="C23" s="1">
         <v>0.13911305366694399</v>
       </c>
-    </row>
-    <row r="24" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="F23" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G23" s="1">
+        <v>8.5801266895029205</v>
+      </c>
+      <c r="H23" s="1">
+        <v>0.14486186097849299</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" s="1" t="s">
         <v>25</v>
       </c>
@@ -8885,8 +10084,17 @@
       <c r="C24" s="1">
         <v>0.136881983671574</v>
       </c>
-    </row>
-    <row r="25" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="F24" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="G24" s="1">
+        <v>8.5783681642005494</v>
+      </c>
+      <c r="H24" s="1">
+        <v>0.14493175120103199</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" s="1" t="s">
         <v>26</v>
       </c>
@@ -8896,8 +10104,17 @@
       <c r="C25" s="1">
         <v>0.135891683439223</v>
       </c>
-    </row>
-    <row r="26" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="F25" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G25" s="1">
+        <v>8.6129268121772302</v>
+      </c>
+      <c r="H25" s="1">
+        <v>0.14335784354365599</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" s="1" t="s">
         <v>27</v>
       </c>
@@ -8907,8 +10124,17 @@
       <c r="C26" s="1">
         <v>0.134600217130598</v>
       </c>
-    </row>
-    <row r="27" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="F26" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G26" s="1">
+        <v>8.6349505815443095</v>
+      </c>
+      <c r="H26" s="1">
+        <v>0.14372426788936199</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" s="1" t="s">
         <v>28</v>
       </c>
@@ -8918,8 +10144,17 @@
       <c r="C27" s="1">
         <v>0.117218052017694</v>
       </c>
-    </row>
-    <row r="28" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="F27" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G27" s="1">
+        <v>8.5827352500219707</v>
+      </c>
+      <c r="H27" s="1">
+        <v>0.140914458888726</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" s="1" t="s">
         <v>29</v>
       </c>
@@ -8929,8 +10164,17 @@
       <c r="C28" s="1">
         <v>0.116738218899043</v>
       </c>
-    </row>
-    <row r="29" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="F28" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G28" s="1">
+        <v>8.6784045244654298</v>
+      </c>
+      <c r="H28" s="1">
+        <v>0.144559929539015</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" s="1" t="s">
         <v>30</v>
       </c>
@@ -8940,8 +10184,17 @@
       <c r="C29" s="1">
         <v>0.116641895814922</v>
       </c>
-    </row>
-    <row r="30" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="F29" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="G29" s="1">
+        <v>8.5889121451567796</v>
+      </c>
+      <c r="H29" s="1">
+        <v>0.13911305366694399</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" s="1" t="s">
         <v>31</v>
       </c>
@@ -8952,7 +10205,7 @@
         <v>0.117986722306339</v>
       </c>
     </row>
-    <row r="31" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:8" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" s="1" t="s">
         <v>32</v>
       </c>
@@ -8963,7 +10216,7 @@
         <v>0.116363944216263</v>
       </c>
     </row>
-    <row r="32" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:8" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" s="1" t="s">
         <v>33</v>
       </c>
@@ -8974,7 +10227,7 @@
         <v>0.117960737624138</v>
       </c>
     </row>
-    <row r="33" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" s="1" t="s">
         <v>34</v>
       </c>
@@ -8985,7 +10238,7 @@
         <v>0.11777189549636199</v>
       </c>
     </row>
-    <row r="34" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A34" s="1" t="s">
         <v>35</v>
       </c>
@@ -8996,7 +10249,7 @@
         <v>0.118362346500101</v>
       </c>
     </row>
-    <row r="35" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A35" s="1" t="s">
         <v>36</v>
       </c>
@@ -9007,7 +10260,7 @@
         <v>0.11875028071223</v>
       </c>
     </row>
-    <row r="36" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A36" s="1" t="s">
         <v>37</v>
       </c>
@@ -9018,7 +10271,7 @@
         <v>0.118209453954305</v>
       </c>
     </row>
-    <row r="37" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" s="1" t="s">
         <v>38</v>
       </c>
@@ -9029,7 +10282,7 @@
         <v>0.116577694816434</v>
       </c>
     </row>
-    <row r="38" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A38" s="1" t="s">
         <v>39</v>
       </c>
@@ -9040,7 +10293,7 @@
         <v>0.117670638852321</v>
       </c>
     </row>
-    <row r="39" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A39" s="1" t="s">
         <v>40</v>
       </c>
@@ -9051,7 +10304,7 @@
         <v>0.118098845799444</v>
       </c>
     </row>
-    <row r="40" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A40" s="1" t="s">
         <v>41</v>
       </c>
@@ -9062,7 +10315,7 @@
         <v>0.11655919684067299</v>
       </c>
     </row>
-    <row r="41" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A41" s="1" t="s">
         <v>42</v>
       </c>
@@ -9073,7 +10326,7 @@
         <v>0.118487075826876</v>
       </c>
     </row>
-    <row r="42" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A42" s="1" t="s">
         <v>43</v>
       </c>
@@ -9084,7 +10337,7 @@
         <v>0.117049111989703</v>
       </c>
     </row>
-    <row r="43" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A43" s="1" t="s">
         <v>44</v>
       </c>
@@ -9095,7 +10348,7 @@
         <v>0.116964493443121</v>
       </c>
     </row>
-    <row r="44" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A44" s="1" t="s">
         <v>45</v>
       </c>
@@ -9106,7 +10359,7 @@
         <v>0.1174932059815</v>
       </c>
     </row>
-    <row r="45" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A45" s="1" t="s">
         <v>46</v>
       </c>
@@ -9117,7 +10370,7 @@
         <v>0.118724780988732</v>
       </c>
     </row>
-    <row r="46" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A46" s="1" t="s">
         <v>47</v>
       </c>
@@ -9128,7 +10381,7 @@
         <v>0.11857414162119</v>
       </c>
     </row>
-    <row r="47" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A47" s="1" t="s">
         <v>48</v>
       </c>
@@ -9139,7 +10392,7 @@
         <v>0.116857985488521</v>
       </c>
     </row>
-    <row r="48" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A48" s="1" t="s">
         <v>49</v>
       </c>
@@ -9150,7 +10403,7 @@
         <v>0.117839930521939</v>
       </c>
     </row>
-    <row r="49" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A49" s="1" t="s">
         <v>50</v>
       </c>
@@ -9161,7 +10414,7 @@
         <v>0.116123290748398</v>
       </c>
     </row>
-    <row r="50" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A50" s="1" t="s">
         <v>51</v>
       </c>
@@ -9172,7 +10425,7 @@
         <v>0.116339626646247</v>
       </c>
     </row>
-    <row r="51" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A51" s="1" t="s">
         <v>52</v>
       </c>
@@ -9183,7 +10436,7 @@
         <v>0.118521454357363</v>
       </c>
     </row>
-    <row r="52" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A52" s="1" t="s">
         <v>53</v>
       </c>
@@ -9194,7 +10447,7 @@
         <v>0.117743388207075</v>
       </c>
     </row>
-    <row r="53" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A53" s="1" t="s">
         <v>54</v>
       </c>
@@ -9205,7 +10458,7 @@
         <v>0.116823099810358</v>
       </c>
     </row>
-    <row r="54" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A54" s="1" t="s">
         <v>55</v>
       </c>
@@ -9216,7 +10469,7 @@
         <v>0.118509294607666</v>
       </c>
     </row>
-    <row r="55" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A55" s="1" t="s">
         <v>56</v>
       </c>
@@ -9227,7 +10480,7 @@
         <v>0.118631007440724</v>
       </c>
     </row>
-    <row r="56" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A56" s="1" t="s">
         <v>57</v>
       </c>
@@ -9238,7 +10491,7 @@
         <v>0.117484320873481</v>
       </c>
     </row>
-    <row r="57" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A57" s="1" t="s">
         <v>58</v>
       </c>
@@ -9249,7 +10502,7 @@
         <v>0.118251546607688</v>
       </c>
     </row>
-    <row r="58" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A58" s="1" t="s">
         <v>59</v>
       </c>
@@ -9260,7 +10513,7 @@
         <v>0.118181098472526</v>
       </c>
     </row>
-    <row r="59" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A59" s="1" t="s">
         <v>60</v>
       </c>
@@ -9271,7 +10524,7 @@
         <v>8.9287039240001795E-2</v>
       </c>
     </row>
-    <row r="60" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A60" s="1" t="s">
         <v>61</v>
       </c>
@@ -9282,7 +10535,7 @@
         <v>8.9953273584561996E-2</v>
       </c>
     </row>
-    <row r="61" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A61" s="1" t="s">
         <v>62</v>
       </c>
@@ -9293,7 +10546,7 @@
         <v>9.1230909809772498E-2</v>
       </c>
     </row>
-    <row r="62" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A62" s="1" t="s">
         <v>63</v>
       </c>
@@ -9304,7 +10557,7 @@
         <v>9.0037965159722497E-2</v>
       </c>
     </row>
-    <row r="63" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A63" s="1" t="s">
         <v>64</v>
       </c>
@@ -9315,7 +10568,7 @@
         <v>9.2063662732121604E-2</v>
       </c>
     </row>
-    <row r="64" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A64" s="1" t="s">
         <v>65</v>
       </c>
@@ -9326,7 +10579,7 @@
         <v>9.0566169869859395E-2</v>
       </c>
     </row>
-    <row r="65" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A65" s="1" t="s">
         <v>66</v>
       </c>
@@ -9337,7 +10590,7 @@
         <v>9.1281359996997199E-2</v>
       </c>
     </row>
-    <row r="66" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A66" s="1" t="s">
         <v>67</v>
       </c>
@@ -9348,7 +10601,7 @@
         <v>9.0246189977935598E-2</v>
       </c>
     </row>
-    <row r="67" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A67" s="1" t="s">
         <v>68</v>
       </c>
@@ -9359,7 +10612,7 @@
         <v>8.7987770056780296E-2</v>
       </c>
     </row>
-    <row r="68" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A68" s="1" t="s">
         <v>69</v>
       </c>
@@ -9370,7 +10623,7 @@
         <v>9.1038024594974204E-2</v>
       </c>
     </row>
-    <row r="69" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A69" s="1" t="s">
         <v>70</v>
       </c>
@@ -9381,7 +10634,7 @@
         <v>9.0356969610468907E-2</v>
       </c>
     </row>
-    <row r="70" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A70" s="1" t="s">
         <v>71</v>
       </c>
@@ -9392,7 +10645,7 @@
         <v>8.9055177802521202E-2</v>
       </c>
     </row>
-    <row r="71" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A71" s="1" t="s">
         <v>72</v>
       </c>
@@ -9403,7 +10656,7 @@
         <v>9.0556231765949805E-2</v>
       </c>
     </row>
-    <row r="72" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A72" s="1" t="s">
         <v>73</v>
       </c>
@@ -9414,7 +10667,7 @@
         <v>9.1259865204828206E-2</v>
       </c>
     </row>
-    <row r="73" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A73" s="1" t="s">
         <v>74</v>
       </c>
@@ -9425,7 +10678,7 @@
         <v>8.8371089308141498E-2</v>
       </c>
     </row>
-    <row r="74" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A74" s="1" t="s">
         <v>75</v>
       </c>
@@ -9436,7 +10689,7 @@
         <v>8.9886315679026302E-2</v>
       </c>
     </row>
-    <row r="75" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A75" s="1" t="s">
         <v>76</v>
       </c>
@@ -9447,7 +10700,7 @@
         <v>0.22378459935658199</v>
       </c>
     </row>
-    <row r="76" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A76" s="1" t="s">
         <v>77</v>
       </c>
@@ -9458,7 +10711,7 @@
         <v>0.228434718604688</v>
       </c>
     </row>
-    <row r="77" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A77" s="1" t="s">
         <v>78</v>
       </c>
@@ -9469,7 +10722,7 @@
         <v>0.221372998488612</v>
       </c>
     </row>
-    <row r="78" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A78" s="1" t="s">
         <v>79</v>
       </c>
@@ -9480,7 +10733,7 @@
         <v>0.225975457594905</v>
       </c>
     </row>
-    <row r="79" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A79" s="1" t="s">
         <v>80</v>
       </c>
@@ -9491,7 +10744,7 @@
         <v>0.225216837741747</v>
       </c>
     </row>
-    <row r="80" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A80" s="1" t="s">
         <v>81</v>
       </c>
@@ -9502,7 +10755,7 @@
         <v>0.229746279532067</v>
       </c>
     </row>
-    <row r="81" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A81" s="1" t="s">
         <v>82</v>
       </c>
@@ -9513,7 +10766,7 @@
         <v>0.22722518963626401</v>
       </c>
     </row>
-    <row r="82" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A82" s="1" t="s">
         <v>83</v>
       </c>
@@ -9524,7 +10777,7 @@
         <v>0.222965184868961</v>
       </c>
     </row>
-    <row r="83" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A83" s="1" t="s">
         <v>84</v>
       </c>
@@ -9535,7 +10788,7 @@
         <v>0.22898718060617901</v>
       </c>
     </row>
-    <row r="84" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A84" s="1" t="s">
         <v>85</v>
       </c>
@@ -9546,7 +10799,7 @@
         <v>0.22580668748875701</v>
       </c>
     </row>
-    <row r="85" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A85" s="1" t="s">
         <v>86</v>
       </c>
@@ -9557,7 +10810,7 @@
         <v>0.231594890582631</v>
       </c>
     </row>
-    <row r="86" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A86" s="1" t="s">
         <v>87</v>
       </c>
@@ -9568,7 +10821,7 @@
         <v>0.224583618990919</v>
       </c>
     </row>
-    <row r="87" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A87" s="1" t="s">
         <v>88</v>
       </c>
@@ -9579,7 +10832,7 @@
         <v>0.23249128317182099</v>
       </c>
     </row>
-    <row r="88" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A88" s="1" t="s">
         <v>89</v>
       </c>
@@ -9590,7 +10843,7 @@
         <v>0.23073510515949899</v>
       </c>
     </row>
-    <row r="89" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A89" s="1" t="s">
         <v>90</v>
       </c>
@@ -9601,7 +10854,7 @@
         <v>0.229179326874075</v>
       </c>
     </row>
-    <row r="90" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A90" s="1" t="s">
         <v>91</v>
       </c>
@@ -9612,7 +10865,7 @@
         <v>0.226024665246639</v>
       </c>
     </row>
-    <row r="91" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A91" s="1" t="s">
         <v>92</v>
       </c>
@@ -9623,7 +10876,7 @@
         <v>0.22988414195496401</v>
       </c>
     </row>
-    <row r="92" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A92" s="1" t="s">
         <v>93</v>
       </c>
@@ -9634,7 +10887,7 @@
         <v>0.22795719930278499</v>
       </c>
     </row>
-    <row r="93" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A93" s="1" t="s">
         <v>94</v>
       </c>
@@ -9645,7 +10898,7 @@
         <v>0.227267035209756</v>
       </c>
     </row>
-    <row r="94" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A94" s="1" t="s">
         <v>95</v>
       </c>
@@ -9656,7 +10909,7 @@
         <v>0.22728875634974799</v>
       </c>
     </row>
-    <row r="95" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A95" s="1" t="s">
         <v>96</v>
       </c>
@@ -9667,7 +10920,7 @@
         <v>0.22819660608103401</v>
       </c>
     </row>
-    <row r="96" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A96" s="1" t="s">
         <v>97</v>
       </c>
@@ -9678,7 +10931,7 @@
         <v>0.22449918198189101</v>
       </c>
     </row>
-    <row r="97" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A97" s="1" t="s">
         <v>98</v>
       </c>
@@ -9689,7 +10942,7 @@
         <v>0.22352994908158599</v>
       </c>
     </row>
-    <row r="98" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A98" s="1" t="s">
         <v>99</v>
       </c>
@@ -9700,7 +10953,7 @@
         <v>0.22753327784977401</v>
       </c>
     </row>
-    <row r="99" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A99" s="1" t="s">
         <v>100</v>
       </c>
@@ -9711,7 +10964,7 @@
         <v>0.22784419865740199</v>
       </c>
     </row>
-    <row r="100" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A100" s="1" t="s">
         <v>101</v>
       </c>
@@ -9722,7 +10975,7 @@
         <v>0.225433003733543</v>
       </c>
     </row>
-    <row r="101" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A101" s="1" t="s">
         <v>102</v>
       </c>
@@ -9733,7 +10986,7 @@
         <v>0.22712348211729699</v>
       </c>
     </row>
-    <row r="102" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A102" s="1" t="s">
         <v>103</v>
       </c>
@@ -9744,7 +10997,7 @@
         <v>0.22894109101944199</v>
       </c>
     </row>
-    <row r="103" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A103" s="1" t="s">
         <v>104</v>
       </c>
@@ -9755,7 +11008,7 @@
         <v>0.23027592968354901</v>
       </c>
     </row>
-    <row r="104" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A104" s="1" t="s">
         <v>105</v>
       </c>
@@ -9766,7 +11019,7 @@
         <v>0.22733899516780401</v>
       </c>
     </row>
-    <row r="105" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A105" s="1" t="s">
         <v>106</v>
       </c>
@@ -9777,7 +11030,7 @@
         <v>0.22718964047891599</v>
       </c>
     </row>
-    <row r="106" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A106" s="1" t="s">
         <v>107</v>
       </c>
@@ -9788,7 +11041,7 @@
         <v>0.22249606599096799</v>
       </c>
     </row>
-    <row r="107" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A107" s="1" t="s">
         <v>108</v>
       </c>
@@ -9799,7 +11052,7 @@
         <v>0.22770140189949001</v>
       </c>
     </row>
-    <row r="108" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A108" s="1" t="s">
         <v>109</v>
       </c>
@@ -9810,7 +11063,7 @@
         <v>0.22467693879523801</v>
       </c>
     </row>
-    <row r="109" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A109" s="1" t="s">
         <v>110</v>
       </c>
@@ -9821,7 +11074,7 @@
         <v>0.22590951148508701</v>
       </c>
     </row>
-    <row r="110" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A110" s="1" t="s">
         <v>111</v>
       </c>
@@ -9832,7 +11085,7 @@
         <v>0.22795873224990801</v>
       </c>
     </row>
-    <row r="111" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A111" s="1" t="s">
         <v>112</v>
       </c>
@@ -9843,7 +11096,7 @@
         <v>0.26064960163891099</v>
       </c>
     </row>
-    <row r="112" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A112" s="1" t="s">
         <v>113</v>
       </c>
@@ -9854,7 +11107,7 @@
         <v>0.25338188968269398</v>
       </c>
     </row>
-    <row r="113" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A113" s="1" t="s">
         <v>114</v>
       </c>
@@ -9865,7 +11118,7 @@
         <v>0.25038094455952498</v>
       </c>
     </row>
-    <row r="114" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A114" s="1" t="s">
         <v>115</v>
       </c>
@@ -9876,7 +11129,7 @@
         <v>0.256215228918099</v>
       </c>
     </row>
-    <row r="115" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A115" s="1" t="s">
         <v>116</v>
       </c>
@@ -9887,7 +11140,7 @@
         <v>0.25483329669185101</v>
       </c>
     </row>
-    <row r="116" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A116" s="1" t="s">
         <v>117</v>
       </c>
@@ -9898,7 +11151,7 @@
         <v>0.25854387484878599</v>
       </c>
     </row>
-    <row r="117" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A117" s="1" t="s">
         <v>118</v>
       </c>
@@ -9909,7 +11162,7 @@
         <v>0.25519336396030601</v>
       </c>
     </row>
-    <row r="118" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A118" s="1" t="s">
         <v>119</v>
       </c>
@@ -9920,7 +11173,7 @@
         <v>0.25663303680948102</v>
       </c>
     </row>
-    <row r="119" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A119" s="1" t="s">
         <v>120</v>
       </c>
@@ -9931,7 +11184,7 @@
         <v>0.25601459599486398</v>
       </c>
     </row>
-    <row r="120" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A120" s="1" t="s">
         <v>121</v>
       </c>
@@ -9942,7 +11195,7 @@
         <v>0.25648553124648299</v>
       </c>
     </row>
-    <row r="121" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A121" s="1" t="s">
         <v>122</v>
       </c>
@@ -9953,7 +11206,7 @@
         <v>0.25339182435774998</v>
       </c>
     </row>
-    <row r="122" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A122" s="1" t="s">
         <v>123</v>
       </c>
@@ -9964,7 +11217,7 @@
         <v>0.26261256236820102</v>
       </c>
     </row>
-    <row r="123" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A123" s="1" t="s">
         <v>124</v>
       </c>
@@ -9975,7 +11228,7 @@
         <v>0.25914013258546797</v>
       </c>
     </row>
-    <row r="124" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A124" s="1" t="s">
         <v>125</v>
       </c>
@@ -9986,7 +11239,7 @@
         <v>0.25187380012057398</v>
       </c>
     </row>
-    <row r="125" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A125" s="1" t="s">
         <v>126</v>
       </c>
@@ -9997,7 +11250,7 @@
         <v>0.25861462842520899</v>
       </c>
     </row>
-    <row r="126" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A126" s="1" t="s">
         <v>127</v>
       </c>
@@ -10008,7 +11261,7 @@
         <v>0.26412000142144099</v>
       </c>
     </row>
-    <row r="127" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A127" s="1" t="s">
         <v>128</v>
       </c>
@@ -10019,7 +11272,7 @@
         <v>0.25505739125523702</v>
       </c>
     </row>
-    <row r="128" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A128" s="1" t="s">
         <v>129</v>
       </c>
@@ -10030,7 +11283,7 @@
         <v>0.25268334549192301</v>
       </c>
     </row>
-    <row r="129" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A129" s="1" t="s">
         <v>130</v>
       </c>
@@ -10041,7 +11294,7 @@
         <v>0.254203134019032</v>
       </c>
     </row>
-    <row r="130" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A130" s="1" t="s">
         <v>131</v>
       </c>
@@ -10052,7 +11305,7 @@
         <v>0.25355249186689299</v>
       </c>
     </row>
-    <row r="131" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A131" s="1" t="s">
         <v>132</v>
       </c>
@@ -10063,7 +11316,7 @@
         <v>0.258640908855092</v>
       </c>
     </row>
-    <row r="132" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A132" s="1" t="s">
         <v>133</v>
       </c>
@@ -10074,7 +11327,7 @@
         <v>0.25176887581155899</v>
       </c>
     </row>
-    <row r="133" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A133" s="1" t="s">
         <v>134</v>
       </c>
@@ -10085,7 +11338,7 @@
         <v>0.25436276153236997</v>
       </c>
     </row>
-    <row r="134" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A134" s="1" t="s">
         <v>135</v>
       </c>
@@ -10096,7 +11349,7 @@
         <v>0.25848980394328103</v>
       </c>
     </row>
-    <row r="135" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A135" s="1" t="s">
         <v>136</v>
       </c>
@@ -10107,7 +11360,7 @@
         <v>0.25493042534243598</v>
       </c>
     </row>
-    <row r="136" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A136" s="1" t="s">
         <v>137</v>
       </c>
@@ -10118,7 +11371,7 @@
         <v>0.25702073078272197</v>
       </c>
     </row>
-    <row r="137" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A137" s="1" t="s">
         <v>138</v>
       </c>
@@ -10129,7 +11382,7 @@
         <v>0.25281370286486299</v>
       </c>
     </row>
-    <row r="138" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A138" s="1" t="s">
         <v>139</v>
       </c>
@@ -10140,7 +11393,7 @@
         <v>0.25787828139437702</v>
       </c>
     </row>
-    <row r="139" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A139" s="1" t="s">
         <v>140</v>
       </c>
@@ -10151,7 +11404,7 @@
         <v>0.255030114263046</v>
       </c>
     </row>
-    <row r="140" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A140" s="1" t="s">
         <v>141</v>
       </c>
@@ -10162,7 +11415,7 @@
         <v>0.25326708245889501</v>
       </c>
     </row>
-    <row r="141" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A141" s="1" t="s">
         <v>142</v>
       </c>
@@ -10173,7 +11426,7 @@
         <v>0.25901851572451601</v>
       </c>
     </row>
-    <row r="142" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A142" s="1" t="s">
         <v>143</v>
       </c>
@@ -10184,7 +11437,7 @@
         <v>0.25402214979933802</v>
       </c>
     </row>
-    <row r="143" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A143" s="1" t="s">
         <v>144</v>
       </c>
@@ -10195,7 +11448,7 @@
         <v>0.25207440807669201</v>
       </c>
     </row>
-    <row r="144" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A144" s="1" t="s">
         <v>145</v>
       </c>
@@ -10206,7 +11459,7 @@
         <v>0.25648835225167999</v>
       </c>
     </row>
-    <row r="145" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A145" s="1" t="s">
         <v>146</v>
       </c>
@@ -10217,7 +11470,7 @@
         <v>0.25619702232418301</v>
       </c>
     </row>
-    <row r="146" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A146" s="1" t="s">
         <v>147</v>
       </c>
@@ -10228,7 +11481,7 @@
         <v>0.256904989972564</v>
       </c>
     </row>
-    <row r="147" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A147" s="1" t="s">
         <v>148</v>
       </c>
@@ -10239,7 +11492,7 @@
         <v>0.25656545981822299</v>
       </c>
     </row>
-    <row r="148" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A148" s="1" t="s">
         <v>149</v>
       </c>
@@ -10250,7 +11503,7 @@
         <v>0.25471437628790899</v>
       </c>
     </row>
-    <row r="149" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A149" s="1" t="s">
         <v>150</v>
       </c>
@@ -10261,7 +11514,7 @@
         <v>0.25564492601438199</v>
       </c>
     </row>
-    <row r="150" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A150" s="1" t="s">
         <v>151</v>
       </c>
@@ -10272,7 +11525,7 @@
         <v>0.26266359379455601</v>
       </c>
     </row>
-    <row r="151" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A151" s="1" t="s">
         <v>152</v>
       </c>
@@ -10283,7 +11536,7 @@
         <v>0.25914186884267898</v>
       </c>
     </row>
-    <row r="152" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A152" s="1" t="s">
         <v>153</v>
       </c>
@@ -10294,7 +11547,7 @@
         <v>0.25621155685651098</v>
       </c>
     </row>
-    <row r="153" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A153" s="1" t="s">
         <v>154</v>
       </c>
@@ -10305,7 +11558,7 @@
         <v>0.25866494788723898</v>
       </c>
     </row>
-    <row r="154" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A154" s="1" t="s">
         <v>155</v>
       </c>
@@ -10316,7 +11569,7 @@
         <v>0.25801756322347102</v>
       </c>
     </row>
-    <row r="155" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A155" s="1" t="s">
         <v>156</v>
       </c>
@@ -10327,7 +11580,7 @@
         <v>0.25944545650678502</v>
       </c>
     </row>
-    <row r="156" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A156" s="1" t="s">
         <v>157</v>
       </c>
@@ -10338,7 +11591,7 @@
         <v>0.25336488450504602</v>
       </c>
     </row>
-    <row r="157" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A157" s="1" t="s">
         <v>158</v>
       </c>
@@ -10349,7 +11602,7 @@
         <v>0.261553420142073</v>
       </c>
     </row>
-    <row r="158" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A158" s="1" t="s">
         <v>159</v>
       </c>
@@ -10360,7 +11613,7 @@
         <v>0.26019522603942802</v>
       </c>
     </row>
-    <row r="159" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A159" s="1" t="s">
         <v>160</v>
       </c>
@@ -10371,7 +11624,7 @@
         <v>0.25868729407005198</v>
       </c>
     </row>
-    <row r="160" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A160" s="1" t="s">
         <v>161</v>
       </c>
@@ -10382,7 +11635,7 @@
         <v>0.25516460879894798</v>
       </c>
     </row>
-    <row r="161" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A161" s="1" t="s">
         <v>162</v>
       </c>
@@ -10393,7 +11646,7 @@
         <v>0.25295075090609098</v>
       </c>
     </row>
-    <row r="162" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A162" s="1" t="s">
         <v>163</v>
       </c>
@@ -10404,7 +11657,7 @@
         <v>0.256452611497334</v>
       </c>
     </row>
-    <row r="163" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A163" s="1" t="s">
         <v>164</v>
       </c>
@@ -10415,7 +11668,7 @@
         <v>0.25868777299010298</v>
       </c>
     </row>
-    <row r="164" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A164" s="1" t="s">
         <v>165</v>
       </c>
@@ -10426,7 +11679,7 @@
         <v>0.2539674766801</v>
       </c>
     </row>
-    <row r="165" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A165" s="1" t="s">
         <v>166</v>
       </c>
@@ -10437,7 +11690,7 @@
         <v>0.17294771128421699</v>
       </c>
     </row>
-    <row r="166" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A166" s="1" t="s">
         <v>167</v>
       </c>
@@ -10448,7 +11701,7 @@
         <v>0.175665485735155</v>
       </c>
     </row>
-    <row r="167" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A167" s="1" t="s">
         <v>168</v>
       </c>
@@ -10459,7 +11712,7 @@
         <v>0.17382778027635701</v>
       </c>
     </row>
-    <row r="168" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A168" s="1" t="s">
         <v>169</v>
       </c>
@@ -10470,7 +11723,7 @@
         <v>0.17455983570099701</v>
       </c>
     </row>
-    <row r="169" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A169" s="1" t="s">
         <v>170</v>
       </c>
@@ -10481,7 +11734,7 @@
         <v>0.17664296551393399</v>
       </c>
     </row>
-    <row r="170" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A170" s="1" t="s">
         <v>171</v>
       </c>
@@ -10492,7 +11745,7 @@
         <v>0.17708531560420199</v>
       </c>
     </row>
-    <row r="171" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A171" s="1" t="s">
         <v>172</v>
       </c>
@@ -10503,7 +11756,7 @@
         <v>0.17557573140333699</v>
       </c>
     </row>
-    <row r="172" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A172" s="1" t="s">
         <v>173</v>
       </c>
@@ -10514,7 +11767,7 @@
         <v>0.173457649972002</v>
       </c>
     </row>
-    <row r="173" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A173" s="1" t="s">
         <v>174</v>
       </c>
@@ -10525,7 +11778,7 @@
         <v>0.17535865105134299</v>
       </c>
     </row>
-    <row r="174" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A174" s="1" t="s">
         <v>175</v>
       </c>
@@ -10536,7 +11789,7 @@
         <v>0.175039518424147</v>
       </c>
     </row>
-    <row r="175" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A175" s="1" t="s">
         <v>176</v>
       </c>
@@ -10547,7 +11800,7 @@
         <v>0.17459939950666101</v>
       </c>
     </row>
-    <row r="176" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A176" s="1" t="s">
         <v>177</v>
       </c>
@@ -10558,7 +11811,7 @@
         <v>0.17177387798819599</v>
       </c>
     </row>
-    <row r="177" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A177" s="1" t="s">
         <v>178</v>
       </c>
@@ -10569,7 +11822,7 @@
         <v>0.172049396498035</v>
       </c>
     </row>
-    <row r="178" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A178" s="1" t="s">
         <v>179</v>
       </c>
@@ -10580,7 +11833,7 @@
         <v>0.17416028353340501</v>
       </c>
     </row>
-    <row r="179" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A179" s="1" t="s">
         <v>180</v>
       </c>
@@ -10591,7 +11844,7 @@
         <v>0.17432866559164001</v>
       </c>
     </row>
-    <row r="180" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A180" s="1" t="s">
         <v>181</v>
       </c>
@@ -10602,7 +11855,7 @@
         <v>0.17371638201273101</v>
       </c>
     </row>
-    <row r="181" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A181" s="1" t="s">
         <v>182</v>
       </c>
@@ -10613,7 +11866,7 @@
         <v>0.17123203171632401</v>
       </c>
     </row>
-    <row r="182" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A182" s="1" t="s">
         <v>183</v>
       </c>
@@ -10624,7 +11877,7 @@
         <v>0.17318569822136001</v>
       </c>
     </row>
-    <row r="183" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A183" s="1" t="s">
         <v>184</v>
       </c>
@@ -10635,7 +11888,7 @@
         <v>0.17669669700448201</v>
       </c>
     </row>
-    <row r="184" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A184" s="1" t="s">
         <v>185</v>
       </c>
@@ -10646,7 +11899,7 @@
         <v>0.17723933870696301</v>
       </c>
     </row>
-    <row r="185" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A185" s="1" t="s">
         <v>186</v>
       </c>
@@ -10657,7 +11910,7 @@
         <v>0.17063092731327101</v>
       </c>
     </row>
-    <row r="186" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A186" s="1" t="s">
         <v>187</v>
       </c>
@@ -10668,7 +11921,7 @@
         <v>0.17490193092626999</v>
       </c>
     </row>
-    <row r="187" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A187" s="1" t="s">
         <v>188</v>
       </c>
@@ -10679,7 +11932,7 @@
         <v>0.17702310390171999</v>
       </c>
     </row>
-    <row r="188" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A188" s="1" t="s">
         <v>189</v>
       </c>
@@ -10690,7 +11943,7 @@
         <v>0.171948853936535</v>
       </c>
     </row>
-    <row r="189" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A189" s="1" t="s">
         <v>190</v>
       </c>
@@ -10701,7 +11954,7 @@
         <v>0.17411860264206899</v>
       </c>
     </row>
-    <row r="190" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A190" s="1" t="s">
         <v>191</v>
       </c>
@@ -10712,7 +11965,7 @@
         <v>0.175935205113702</v>
       </c>
     </row>
-    <row r="191" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A191" s="1" t="s">
         <v>192</v>
       </c>
@@ -10723,7 +11976,7 @@
         <v>0.17427622300988699</v>
       </c>
     </row>
-    <row r="192" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A192" s="1" t="s">
         <v>193</v>
       </c>
@@ -10734,7 +11987,7 @@
         <v>0.17224969239811899</v>
       </c>
     </row>
-    <row r="193" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A193" s="1" t="s">
         <v>194</v>
       </c>
@@ -10745,7 +11998,7 @@
         <v>0.17435257559575301</v>
       </c>
     </row>
-    <row r="194" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A194" s="1" t="s">
         <v>195</v>
       </c>
@@ -10756,7 +12009,7 @@
         <v>0.171222354567128</v>
       </c>
     </row>
-    <row r="195" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A195" s="1" t="s">
         <v>196</v>
       </c>
@@ -10767,7 +12020,7 @@
         <v>0.17230494746765301</v>
       </c>
     </row>
-    <row r="196" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A196" s="1" t="s">
         <v>197</v>
       </c>
@@ -10778,7 +12031,7 @@
         <v>0.17976030708667101</v>
       </c>
     </row>
-    <row r="197" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A197" s="1" t="s">
         <v>198</v>
       </c>
@@ -10789,7 +12042,7 @@
         <v>0.174433801903358</v>
       </c>
     </row>
-    <row r="198" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A198" s="1" t="s">
         <v>199</v>
       </c>
@@ -10800,7 +12053,7 @@
         <v>0.17714435708530099</v>
       </c>
     </row>
-    <row r="199" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A199" s="1" t="s">
         <v>200</v>
       </c>
@@ -10811,7 +12064,7 @@
         <v>0.17086804073973499</v>
       </c>
     </row>
-    <row r="200" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A200" s="1" t="s">
         <v>201</v>
       </c>
@@ -10822,7 +12075,7 @@
         <v>0.171697248433512</v>
       </c>
     </row>
-    <row r="201" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A201" s="1" t="s">
         <v>202</v>
       </c>
@@ -10833,7 +12086,7 @@
         <v>0.17443666559002999</v>
       </c>
     </row>
-    <row r="202" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A202" s="1" t="s">
         <v>203</v>
       </c>
@@ -10844,7 +12097,7 @@
         <v>0.17690051952166999</v>
       </c>
     </row>
-    <row r="203" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A203" s="1" t="s">
         <v>204</v>
       </c>
@@ -10855,19 +12108,19 @@
         <v>0.17654554655181801</v>
       </c>
     </row>
-    <row r="204" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="B204" s="1"/>
       <c r="C204" s="1"/>
     </row>
-    <row r="205" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="B205" s="1"/>
       <c r="C205" s="1"/>
     </row>
-    <row r="206" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="B206" s="1"/>
       <c r="C206" s="1"/>
     </row>
-    <row r="207" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A207" s="1" t="s">
         <v>205</v>
       </c>
@@ -10878,7 +12131,7 @@
         <v>0.21689563024651701</v>
       </c>
     </row>
-    <row r="208" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A208" s="1" t="s">
         <v>206</v>
       </c>
@@ -10889,7 +12142,7 @@
         <v>0.21250705902688999</v>
       </c>
     </row>
-    <row r="209" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A209" s="1" t="s">
         <v>207</v>
       </c>
@@ -10900,7 +12153,7 @@
         <v>0.21268324019514501</v>
       </c>
     </row>
-    <row r="210" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A210" s="1" t="s">
         <v>208</v>
       </c>
@@ -10911,7 +12164,7 @@
         <v>0.21049345542616399</v>
       </c>
     </row>
-    <row r="211" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A211" s="1" t="s">
         <v>209</v>
       </c>
@@ -10922,7 +12175,7 @@
         <v>0.214431740824571</v>
       </c>
     </row>
-    <row r="212" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A212" s="1" t="s">
         <v>210</v>
       </c>
@@ -10933,7 +12186,7 @@
         <v>0.21026943516751501</v>
       </c>
     </row>
-    <row r="213" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A213" s="1" t="s">
         <v>211</v>
       </c>
@@ -10944,7 +12197,7 @@
         <v>0.211983108185162</v>
       </c>
     </row>
-    <row r="214" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A214" s="1" t="s">
         <v>212</v>
       </c>
@@ -10955,7 +12208,7 @@
         <v>0.212540414406241</v>
       </c>
     </row>
-    <row r="215" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A215" s="1" t="s">
         <v>213</v>
       </c>
@@ -10966,7 +12219,7 @@
         <v>0.21316933311979799</v>
       </c>
     </row>
-    <row r="216" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A216" s="1" t="s">
         <v>214</v>
       </c>
@@ -10977,7 +12230,7 @@
         <v>0.212515123863107</v>
       </c>
     </row>
-    <row r="217" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A217" s="1" t="s">
         <v>215</v>
       </c>
@@ -10988,7 +12241,7 @@
         <v>0.21030240285409901</v>
       </c>
     </row>
-    <row r="218" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A218" s="1" t="s">
         <v>216</v>
       </c>
@@ -10999,7 +12252,7 @@
         <v>0.213000429148374</v>
       </c>
     </row>
-    <row r="219" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A219" s="1" t="s">
         <v>217</v>
       </c>
@@ -11010,7 +12263,7 @@
         <v>0.21204120218539499</v>
       </c>
     </row>
-    <row r="220" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A220" s="1" t="s">
         <v>218</v>
       </c>
@@ -11021,7 +12274,7 @@
         <v>0.211005527878392</v>
       </c>
     </row>
-    <row r="221" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A221" s="1" t="s">
         <v>219</v>
       </c>
@@ -11032,7 +12285,7 @@
         <v>0.21490935202097999</v>
       </c>
     </row>
-    <row r="222" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A222" s="1" t="s">
         <v>220</v>
       </c>
@@ -11043,7 +12296,7 @@
         <v>0.214705500945685</v>
       </c>
     </row>
-    <row r="223" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A223" s="1" t="s">
         <v>221</v>
       </c>
@@ -11054,7 +12307,7 @@
         <v>0.21046954774395399</v>
       </c>
     </row>
-    <row r="224" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A224" s="1" t="s">
         <v>222</v>
       </c>
@@ -11065,7 +12318,7 @@
         <v>0.212979730482002</v>
       </c>
     </row>
-    <row r="225" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A225" s="1" t="s">
         <v>223</v>
       </c>
@@ -11076,7 +12329,7 @@
         <v>0.21145441547031901</v>
       </c>
     </row>
-    <row r="226" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A226" s="1" t="s">
         <v>224</v>
       </c>
@@ -11087,7 +12340,7 @@
         <v>0.21334229216903</v>
       </c>
     </row>
-    <row r="227" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A227" s="1" t="s">
         <v>225</v>
       </c>
@@ -11098,7 +12351,7 @@
         <v>0.21313225436689001</v>
       </c>
     </row>
-    <row r="228" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A228" s="1" t="s">
         <v>226</v>
       </c>
@@ -11109,7 +12362,7 @@
         <v>0.21364986681269199</v>
       </c>
     </row>
-    <row r="229" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A229" s="1" t="s">
         <v>227</v>
       </c>
@@ -11120,7 +12373,7 @@
         <v>0.21046298569896901</v>
       </c>
     </row>
-    <row r="230" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A230" s="1" t="s">
         <v>228</v>
       </c>
@@ -11131,7 +12384,7 @@
         <v>0.21370475343700501</v>
       </c>
     </row>
-    <row r="231" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A231" s="1" t="s">
         <v>229</v>
       </c>
@@ -11142,7 +12395,7 @@
         <v>0.213427613164866</v>
       </c>
     </row>
-    <row r="232" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A232" s="1" t="s">
         <v>230</v>
       </c>
@@ -11153,7 +12406,7 @@
         <v>0.21285885222227299</v>
       </c>
     </row>
-    <row r="233" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A233" s="1" t="s">
         <v>231</v>
       </c>
@@ -11164,7 +12417,7 @@
         <v>0.21229610722325801</v>
       </c>
     </row>
-    <row r="234" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A234" s="1" t="s">
         <v>232</v>
       </c>
@@ -11175,7 +12428,7 @@
         <v>0.213479995323273</v>
       </c>
     </row>
-    <row r="235" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A235" s="1" t="s">
         <v>233</v>
       </c>
@@ -11186,7 +12439,7 @@
         <v>0.23747635372092801</v>
       </c>
     </row>
-    <row r="236" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A236" s="1" t="s">
         <v>234</v>
       </c>
@@ -11197,7 +12450,7 @@
         <v>0.24180291421483799</v>
       </c>
     </row>
-    <row r="237" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A237" s="1" t="s">
         <v>235</v>
       </c>
@@ -11208,7 +12461,7 @@
         <v>0.23775144209915899</v>
       </c>
     </row>
-    <row r="238" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A238" s="1" t="s">
         <v>236</v>
       </c>
@@ -11219,7 +12472,7 @@
         <v>0.24065215342237201</v>
       </c>
     </row>
-    <row r="239" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A239" s="1" t="s">
         <v>237</v>
       </c>
@@ -11230,7 +12483,7 @@
         <v>0.238634580986853</v>
       </c>
     </row>
-    <row r="240" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A240" s="1" t="s">
         <v>238</v>
       </c>
@@ -11241,7 +12494,7 @@
         <v>0.24123516367901099</v>
       </c>
     </row>
-    <row r="241" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A241" s="1" t="s">
         <v>239</v>
       </c>
@@ -11252,7 +12505,7 @@
         <v>0.23838761262462899</v>
       </c>
     </row>
-    <row r="242" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A242" s="1" t="s">
         <v>240</v>
       </c>
@@ -11263,7 +12516,7 @@
         <v>0.23787175668006799</v>
       </c>
     </row>
-    <row r="243" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A243" s="1" t="s">
         <v>241</v>
       </c>
@@ -11274,7 +12527,7 @@
         <v>0.235957408677299</v>
       </c>
     </row>
-    <row r="244" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A244" s="1" t="s">
         <v>242</v>
       </c>
@@ -11285,7 +12538,7 @@
         <v>0.23761103430247099</v>
       </c>
     </row>
-    <row r="245" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A245" s="1" t="s">
         <v>243</v>
       </c>
@@ -11296,7 +12549,7 @@
         <v>0.24049928819975</v>
       </c>
     </row>
-    <row r="246" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A246" s="1" t="s">
         <v>244</v>
       </c>
@@ -11307,7 +12560,7 @@
         <v>0.23875237313230799</v>
       </c>
     </row>
-    <row r="247" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A247" s="1" t="s">
         <v>245</v>
       </c>
@@ -11318,7 +12571,7 @@
         <v>0.23577509684512599</v>
       </c>
     </row>
-    <row r="248" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A248" s="1" t="s">
         <v>246</v>
       </c>
@@ -11329,7 +12582,7 @@
         <v>0.23798590162913699</v>
       </c>
     </row>
-    <row r="249" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A249" s="1" t="s">
         <v>247</v>
       </c>
@@ -11340,7 +12593,7 @@
         <v>0.23776270729380899</v>
       </c>
     </row>
-    <row r="250" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A250" s="1" t="s">
         <v>248</v>
       </c>
@@ -11351,7 +12604,7 @@
         <v>0.23525871098023601</v>
       </c>
     </row>
-    <row r="251" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A251" s="1" t="s">
         <v>249</v>
       </c>
@@ -11362,7 +12615,7 @@
         <v>0.23822698567085801</v>
       </c>
     </row>
-    <row r="252" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A252" s="1" t="s">
         <v>250</v>
       </c>
@@ -11373,7 +12626,7 @@
         <v>0.236137249858582</v>
       </c>
     </row>
-    <row r="253" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A253" s="1" t="s">
         <v>251</v>
       </c>
@@ -11384,7 +12637,7 @@
         <v>0.236589149526167</v>
       </c>
     </row>
-    <row r="254" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A254" s="1" t="s">
         <v>252</v>
       </c>
@@ -11395,7 +12648,7 @@
         <v>0.234995035195148</v>
       </c>
     </row>
-    <row r="255" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A255" s="1" t="s">
         <v>253</v>
       </c>
@@ -11406,7 +12659,7 @@
         <v>0.238435257488993</v>
       </c>
     </row>
-    <row r="256" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A256" s="1" t="s">
         <v>254</v>
       </c>
@@ -11417,7 +12670,7 @@
         <v>0.23631298859917599</v>
       </c>
     </row>
-    <row r="257" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A257" s="1" t="s">
         <v>255</v>
       </c>
@@ -11428,7 +12681,7 @@
         <v>0.238968925765909</v>
       </c>
     </row>
-    <row r="258" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A258" s="1" t="s">
         <v>256</v>
       </c>
@@ -11439,7 +12692,7 @@
         <v>0.237506075673066</v>
       </c>
     </row>
-    <row r="259" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A259" s="1" t="s">
         <v>257</v>
       </c>
@@ -11450,35 +12703,346 @@
         <v>0.237718713583811</v>
       </c>
     </row>
-    <row r="260" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A260" s="1"/>
-      <c r="B260" s="1"/>
-      <c r="C260" s="1"/>
-    </row>
-    <row r="261" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A261" s="1"/>
-      <c r="B261" s="1"/>
-      <c r="C261" s="1"/>
-    </row>
-    <row r="262" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A262" s="1"/>
-      <c r="B262" s="1"/>
-      <c r="C262" s="1"/>
-    </row>
-    <row r="263" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A263" s="1"/>
-      <c r="B263" s="1"/>
-      <c r="C263" s="1"/>
-    </row>
-    <row r="264" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A264" s="1"/>
-      <c r="B264" s="1"/>
-      <c r="C264" s="1"/>
-    </row>
-    <row r="265" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A265" s="1"/>
-      <c r="B265" s="1"/>
-      <c r="C265" s="1"/>
+    <row r="260" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A260" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="B260" s="1">
+        <v>17.825013007136501</v>
+      </c>
+      <c r="C260" s="1">
+        <v>0.29193451692567801</v>
+      </c>
+    </row>
+    <row r="261" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A261" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="B261" s="1">
+        <v>17.9319730766783</v>
+      </c>
+      <c r="C261" s="1">
+        <v>0.28873287738484599</v>
+      </c>
+    </row>
+    <row r="262" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A262" s="1" t="s">
+        <v>389</v>
+      </c>
+      <c r="B262" s="1">
+        <v>18.039044650769</v>
+      </c>
+      <c r="C262" s="1">
+        <v>0.28985427653153101</v>
+      </c>
+    </row>
+    <row r="263" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A263" s="1" t="s">
+        <v>390</v>
+      </c>
+      <c r="B263" s="1">
+        <v>18.0604756933053</v>
+      </c>
+      <c r="C263" s="1">
+        <v>0.29473582812057803</v>
+      </c>
+    </row>
+    <row r="264" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A264" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="B264" s="1">
+        <v>17.9979172106978</v>
+      </c>
+      <c r="C264" s="1">
+        <v>0.29630016894823502</v>
+      </c>
+    </row>
+    <row r="265" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A265" s="1" t="s">
+        <v>392</v>
+      </c>
+      <c r="B265" s="1">
+        <v>17.998827423434999</v>
+      </c>
+      <c r="C265" s="1">
+        <v>0.290375757335809</v>
+      </c>
+    </row>
+    <row r="266" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A266" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="B266" s="1">
+        <v>18.041509768701101</v>
+      </c>
+      <c r="C266" s="1">
+        <v>0.29184259037329402</v>
+      </c>
+    </row>
+    <row r="267" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A267" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="B267" s="1">
+        <v>18.113057907959</v>
+      </c>
+      <c r="C267" s="1">
+        <v>0.29495272762742802</v>
+      </c>
+    </row>
+    <row r="268" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A268" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="B268" s="1">
+        <v>18.000340035364701</v>
+      </c>
+      <c r="C268" s="1">
+        <v>0.29546767207366198</v>
+      </c>
+    </row>
+    <row r="269" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A269" s="1" t="s">
+        <v>396</v>
+      </c>
+      <c r="B269" s="1">
+        <v>18.056008326627001</v>
+      </c>
+      <c r="C269" s="1">
+        <v>0.29613521382059799</v>
+      </c>
+    </row>
+    <row r="270" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A270" s="1" t="s">
+        <v>397</v>
+      </c>
+      <c r="B270" s="1">
+        <v>18.143480906181601</v>
+      </c>
+      <c r="C270" s="1">
+        <v>0.29582825670155199</v>
+      </c>
+    </row>
+    <row r="271" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A271" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="B271" s="1">
+        <v>18.0505063076521</v>
+      </c>
+      <c r="C271" s="1">
+        <v>0.29449530569974303</v>
+      </c>
+    </row>
+    <row r="272" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A272" s="1" t="s">
+        <v>399</v>
+      </c>
+      <c r="B272" s="1">
+        <v>17.975837914720699</v>
+      </c>
+      <c r="C272" s="1">
+        <v>0.29806425275037302</v>
+      </c>
+    </row>
+    <row r="273" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A273" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="B273" s="1">
+        <v>17.958408612980101</v>
+      </c>
+      <c r="C273" s="1">
+        <v>0.29361605170472399</v>
+      </c>
+    </row>
+    <row r="274" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A274" s="1" t="s">
+        <v>401</v>
+      </c>
+      <c r="B274" s="1">
+        <v>18.089794941394199</v>
+      </c>
+      <c r="C274" s="1">
+        <v>0.29750345759486801</v>
+      </c>
+    </row>
+    <row r="275" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A275" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="B275" s="1">
+        <v>18.011107051113001</v>
+      </c>
+      <c r="C275" s="1">
+        <v>0.29221770492358401</v>
+      </c>
+    </row>
+    <row r="276" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A276" s="1" t="s">
+        <v>403</v>
+      </c>
+      <c r="B276" s="1">
+        <v>18.059805482066999</v>
+      </c>
+      <c r="C276" s="1">
+        <v>0.29462962623990302</v>
+      </c>
+    </row>
+    <row r="277" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A277" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="B277" s="1">
+        <v>17.9483749982906</v>
+      </c>
+      <c r="C277" s="1">
+        <v>0.29592312403825599</v>
+      </c>
+    </row>
+    <row r="278" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A278" s="1" t="s">
+        <v>405</v>
+      </c>
+      <c r="B278" s="1">
+        <v>17.986594818813899</v>
+      </c>
+      <c r="C278" s="1">
+        <v>0.29448024773360298</v>
+      </c>
+    </row>
+    <row r="279" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A279" s="1" t="s">
+        <v>406</v>
+      </c>
+      <c r="B279" s="1">
+        <v>18.0136321630971</v>
+      </c>
+      <c r="C279" s="1">
+        <v>0.29587930445673999</v>
+      </c>
+    </row>
+    <row r="280" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A280" s="1" t="s">
+        <v>407</v>
+      </c>
+      <c r="B280" s="1">
+        <v>18.175378572568899</v>
+      </c>
+      <c r="C280" s="1">
+        <v>0.28842517989208999</v>
+      </c>
+    </row>
+    <row r="281" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A281" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="B281" s="1">
+        <v>18.118575471661899</v>
+      </c>
+      <c r="C281" s="1">
+        <v>0.29360342062414901</v>
+      </c>
+    </row>
+    <row r="282" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A282" s="1" t="s">
+        <v>409</v>
+      </c>
+      <c r="B282" s="1">
+        <v>17.929983986435602</v>
+      </c>
+      <c r="C282" s="1">
+        <v>0.28921987206488498</v>
+      </c>
+    </row>
+    <row r="283" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A283" s="1" t="s">
+        <v>410</v>
+      </c>
+      <c r="B283" s="1">
+        <v>18.106604307150199</v>
+      </c>
+      <c r="C283" s="1">
+        <v>0.29134851176696303</v>
+      </c>
+    </row>
+    <row r="284" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A284" s="1" t="s">
+        <v>411</v>
+      </c>
+      <c r="B284" s="1">
+        <v>17.996855885347902</v>
+      </c>
+      <c r="C284" s="1">
+        <v>0.29264779346075898</v>
+      </c>
+    </row>
+    <row r="285" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A285" s="1" t="s">
+        <v>412</v>
+      </c>
+      <c r="B285" s="1">
+        <v>18.121396667491499</v>
+      </c>
+      <c r="C285" s="1">
+        <v>0.28825504808202801</v>
+      </c>
+    </row>
+    <row r="286" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A286" s="1" t="s">
+        <v>413</v>
+      </c>
+      <c r="B286" s="1">
+        <v>18.094216738234799</v>
+      </c>
+      <c r="C286" s="1">
+        <v>0.29422715038680303</v>
+      </c>
+    </row>
+    <row r="287" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A287" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="B287" s="1">
+        <v>18.1174045096291</v>
+      </c>
+      <c r="C287" s="1">
+        <v>0.295993095562951</v>
+      </c>
+    </row>
+    <row r="288" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A288" s="1" t="s">
+        <v>415</v>
+      </c>
+      <c r="B288" s="1">
+        <v>17.975345051957699</v>
+      </c>
+      <c r="C288" s="1">
+        <v>0.291643296428021</v>
+      </c>
+    </row>
+    <row r="289" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A289" s="1" t="s">
+        <v>416</v>
+      </c>
+      <c r="B289" s="1">
+        <v>18.0641154539816</v>
+      </c>
+      <c r="C289" s="1">
+        <v>0.29408431924388001</v>
+      </c>
+    </row>
+    <row r="290" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A290" s="1" t="s">
+        <v>417</v>
+      </c>
+      <c r="B290" s="1">
+        <v>18.268545430641002</v>
+      </c>
+      <c r="C290" s="1">
+        <v>0.29215304331091801</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -11489,9 +13053,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{50FB9BA1-1961-4714-B0B7-8B6F37F6875A}">
   <dimension ref="A1:C125"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <sheetData>
-    <row r="1" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -11502,7 +13066,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="1" t="s">
         <v>258</v>
       </c>
@@ -11513,7 +13077,7 @@
         <v>0.13284709830915301</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="1" t="s">
         <v>259</v>
       </c>
@@ -11524,7 +13088,7 @@
         <v>0.13179599174591999</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="1" t="s">
         <v>260</v>
       </c>
@@ -11535,7 +13099,7 @@
         <v>0.13701539714226199</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="1" t="s">
         <v>261</v>
       </c>
@@ -11546,7 +13110,7 @@
         <v>0.13611960900852699</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="1" t="s">
         <v>262</v>
       </c>
@@ -11557,7 +13121,7 @@
         <v>0.13627945937632699</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="1" t="s">
         <v>263</v>
       </c>
@@ -11568,7 +13132,7 @@
         <v>0.30390235043574698</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="1" t="s">
         <v>264</v>
       </c>
@@ -11579,7 +13143,7 @@
         <v>0.30438419283964002</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="1" t="s">
         <v>265</v>
       </c>
@@ -11590,7 +13154,7 @@
         <v>0.297161130585052</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="1" t="s">
         <v>266</v>
       </c>
@@ -11601,7 +13165,7 @@
         <v>0.30092447877826201</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="1" t="s">
         <v>267</v>
       </c>
@@ -11612,7 +13176,7 @@
         <v>0.30225556251139701</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="1" t="s">
         <v>268</v>
       </c>
@@ -11623,7 +13187,7 @@
         <v>0.30453505035585898</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="1" t="s">
         <v>269</v>
       </c>
@@ -11634,7 +13198,7 @@
         <v>0.29441937543381203</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="1" t="s">
         <v>270</v>
       </c>
@@ -11645,7 +13209,7 @@
         <v>0.29938049893952201</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="1" t="s">
         <v>271</v>
       </c>
@@ -11656,7 +13220,7 @@
         <v>0.30198767465833298</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="1" t="s">
         <v>272</v>
       </c>
@@ -11667,7 +13231,7 @@
         <v>0.29452133244947898</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="1" t="s">
         <v>273</v>
       </c>
@@ -11678,7 +13242,7 @@
         <v>0.30226636207287</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="1" t="s">
         <v>274</v>
       </c>
@@ -11689,7 +13253,7 @@
         <v>0.30276185184620003</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="1" t="s">
         <v>275</v>
       </c>
@@ -11700,7 +13264,7 @@
         <v>0.30565983998385898</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="1" t="s">
         <v>276</v>
       </c>
@@ -11711,7 +13275,7 @@
         <v>0.30235700258888798</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" s="1" t="s">
         <v>277</v>
       </c>
@@ -11722,7 +13286,7 @@
         <v>0.30470031507930101</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="1" t="s">
         <v>278</v>
       </c>
@@ -11733,7 +13297,7 @@
         <v>0.30681032275950298</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" s="1" t="s">
         <v>279</v>
       </c>
@@ -11744,7 +13308,7 @@
         <v>0.31003085423784599</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" s="1" t="s">
         <v>280</v>
       </c>
@@ -11755,7 +13319,7 @@
         <v>0.30130891367381502</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" s="1" t="s">
         <v>281</v>
       </c>
@@ -11766,7 +13330,7 @@
         <v>0.141175020925183</v>
       </c>
     </row>
-    <row r="26" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" s="1" t="s">
         <v>282</v>
       </c>
@@ -11777,7 +13341,7 @@
         <v>0.13910706901585701</v>
       </c>
     </row>
-    <row r="27" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" s="1" t="s">
         <v>283</v>
       </c>
@@ -11788,7 +13352,7 @@
         <v>0.14173595580689399</v>
       </c>
     </row>
-    <row r="28" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" s="1" t="s">
         <v>284</v>
       </c>
@@ -11799,7 +13363,7 @@
         <v>0.141258173819516</v>
       </c>
     </row>
-    <row r="29" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" s="1" t="s">
         <v>285</v>
       </c>
@@ -11810,7 +13374,7 @@
         <v>0.142207734258748</v>
       </c>
     </row>
-    <row r="30" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" s="1" t="s">
         <v>286</v>
       </c>
@@ -11821,7 +13385,7 @@
         <v>0.13801119003128501</v>
       </c>
     </row>
-    <row r="31" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" s="1" t="s">
         <v>287</v>
       </c>
@@ -11832,7 +13396,7 @@
         <v>0.14302506923553299</v>
       </c>
     </row>
-    <row r="32" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" s="1" t="s">
         <v>288</v>
       </c>
@@ -11843,7 +13407,7 @@
         <v>0.171876620266287</v>
       </c>
     </row>
-    <row r="33" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" s="1" t="s">
         <v>289</v>
       </c>
@@ -11854,7 +13418,7 @@
         <v>0.17507983789020901</v>
       </c>
     </row>
-    <row r="34" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A34" s="1" t="s">
         <v>290</v>
       </c>
@@ -11865,7 +13429,7 @@
         <v>0.17353748848485201</v>
       </c>
     </row>
-    <row r="35" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A35" s="1" t="s">
         <v>291</v>
       </c>
@@ -11876,7 +13440,7 @@
         <v>0.17399520336378199</v>
       </c>
     </row>
-    <row r="36" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A36" s="1" t="s">
         <v>292</v>
       </c>
@@ -11887,7 +13451,7 @@
         <v>0.16979104098602099</v>
       </c>
     </row>
-    <row r="37" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" s="1" t="s">
         <v>293</v>
       </c>
@@ -11898,7 +13462,7 @@
         <v>0.175682517244173</v>
       </c>
     </row>
-    <row r="38" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A38" s="1" t="s">
         <v>294</v>
       </c>
@@ -11909,7 +13473,7 @@
         <v>0.17111359499762699</v>
       </c>
     </row>
-    <row r="39" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A39" s="1" t="s">
         <v>295</v>
       </c>
@@ -11920,7 +13484,7 @@
         <v>0.174442312499583</v>
       </c>
     </row>
-    <row r="40" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A40" s="1" t="s">
         <v>296</v>
       </c>
@@ -11931,7 +13495,7 @@
         <v>0.17165345419397299</v>
       </c>
     </row>
-    <row r="41" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A41" s="1" t="s">
         <v>297</v>
       </c>
@@ -11942,7 +13506,7 @@
         <v>0.17188594050678699</v>
       </c>
     </row>
-    <row r="42" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A42" s="1" t="s">
         <v>298</v>
       </c>
@@ -11953,7 +13517,7 @@
         <v>0.17182639857690499</v>
       </c>
     </row>
-    <row r="43" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A43" s="1" t="s">
         <v>299</v>
       </c>
@@ -11964,7 +13528,7 @@
         <v>0.173011271970926</v>
       </c>
     </row>
-    <row r="44" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A44" s="1" t="s">
         <v>300</v>
       </c>
@@ -11975,7 +13539,7 @@
         <v>0.173393882992014</v>
       </c>
     </row>
-    <row r="45" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A45" s="1" t="s">
         <v>301</v>
       </c>
@@ -11986,7 +13550,7 @@
         <v>0.17255170638235601</v>
       </c>
     </row>
-    <row r="46" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A46" s="1" t="s">
         <v>302</v>
       </c>
@@ -11997,7 +13561,7 @@
         <v>0.176156057962948</v>
       </c>
     </row>
-    <row r="47" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A47" s="1" t="s">
         <v>303</v>
       </c>
@@ -12008,7 +13572,7 @@
         <v>0.17277891898827699</v>
       </c>
     </row>
-    <row r="48" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A48" s="1" t="s">
         <v>304</v>
       </c>
@@ -12019,7 +13583,7 @@
         <v>0.173614948750792</v>
       </c>
     </row>
-    <row r="49" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A49" s="1" t="s">
         <v>305</v>
       </c>
@@ -12030,7 +13594,7 @@
         <v>0.17607067167010601</v>
       </c>
     </row>
-    <row r="50" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A50" s="1" t="s">
         <v>306</v>
       </c>
@@ -12041,7 +13605,7 @@
         <v>0.17040120856414201</v>
       </c>
     </row>
-    <row r="51" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A51" s="1" t="s">
         <v>307</v>
       </c>
@@ -12052,7 +13616,7 @@
         <v>0.17423160269966501</v>
       </c>
     </row>
-    <row r="52" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A52" s="1" t="s">
         <v>308</v>
       </c>
@@ -12063,7 +13627,7 @@
         <v>0.174369956316375</v>
       </c>
     </row>
-    <row r="53" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A53" s="1" t="s">
         <v>309</v>
       </c>
@@ -12074,7 +13638,7 @@
         <v>0.17111424613243301</v>
       </c>
     </row>
-    <row r="54" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A54" s="1" t="s">
         <v>310</v>
       </c>
@@ -12085,7 +13649,7 @@
         <v>0.174141819699693</v>
       </c>
     </row>
-    <row r="55" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A55" s="1" t="s">
         <v>311</v>
       </c>
@@ -12096,7 +13660,7 @@
         <v>0.17027613633024699</v>
       </c>
     </row>
-    <row r="56" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A56" s="1" t="s">
         <v>312</v>
       </c>
@@ -12107,7 +13671,7 @@
         <v>0.17305899861083601</v>
       </c>
     </row>
-    <row r="57" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A57" s="1" t="s">
         <v>313</v>
       </c>
@@ -12118,7 +13682,7 @@
         <v>0.169629744786672</v>
       </c>
     </row>
-    <row r="58" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A58" s="1" t="s">
         <v>314</v>
       </c>
@@ -12129,7 +13693,7 @@
         <v>0.17362236751906199</v>
       </c>
     </row>
-    <row r="59" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A59" s="1" t="s">
         <v>315</v>
       </c>
@@ -12140,7 +13704,7 @@
         <v>0.17378947989454699</v>
       </c>
     </row>
-    <row r="60" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A60" s="1" t="s">
         <v>316</v>
       </c>
@@ -12151,7 +13715,7 @@
         <v>0.17301730214639</v>
       </c>
     </row>
-    <row r="61" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A61" s="1" t="s">
         <v>317</v>
       </c>
@@ -12162,7 +13726,7 @@
         <v>0.17294290042990301</v>
       </c>
     </row>
-    <row r="62" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A62" s="1" t="s">
         <v>318</v>
       </c>
@@ -12173,7 +13737,7 @@
         <v>0.17314296764265499</v>
       </c>
     </row>
-    <row r="63" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A63" s="1" t="s">
         <v>319</v>
       </c>
@@ -12184,7 +13748,7 @@
         <v>0.26702709086345899</v>
       </c>
     </row>
-    <row r="64" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A64" s="1" t="s">
         <v>320</v>
       </c>
@@ -12195,7 +13759,7 @@
         <v>0.26377604366503299</v>
       </c>
     </row>
-    <row r="65" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A65" s="1" t="s">
         <v>321</v>
       </c>
@@ -12206,7 +13770,7 @@
         <v>0.26272554597887199</v>
       </c>
     </row>
-    <row r="66" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A66" s="1" t="s">
         <v>322</v>
       </c>
@@ -12217,7 +13781,7 @@
         <v>0.26788317969509901</v>
       </c>
     </row>
-    <row r="67" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A67" s="1" t="s">
         <v>323</v>
       </c>
@@ -12228,7 +13792,7 @@
         <v>0.26503400399869398</v>
       </c>
     </row>
-    <row r="68" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A68" s="1" t="s">
         <v>324</v>
       </c>
@@ -12239,7 +13803,7 @@
         <v>0.26673897966627602</v>
       </c>
     </row>
-    <row r="69" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A69" s="1" t="s">
         <v>325</v>
       </c>
@@ -12250,7 +13814,7 @@
         <v>0.26807575946030698</v>
       </c>
     </row>
-    <row r="70" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A70" s="1" t="s">
         <v>326</v>
       </c>
@@ -12261,7 +13825,7 @@
         <v>0.266570039729353</v>
       </c>
     </row>
-    <row r="71" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A71" s="1" t="s">
         <v>327</v>
       </c>
@@ -12272,7 +13836,7 @@
         <v>0.27166172606546901</v>
       </c>
     </row>
-    <row r="72" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A72" s="1" t="s">
         <v>328</v>
       </c>
@@ -12283,7 +13847,7 @@
         <v>0.26522605962651602</v>
       </c>
     </row>
-    <row r="73" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A73" s="1" t="s">
         <v>329</v>
       </c>
@@ -12294,7 +13858,7 @@
         <v>0.27094063293660098</v>
       </c>
     </row>
-    <row r="74" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A74" s="1" t="s">
         <v>330</v>
       </c>
@@ -12305,7 +13869,7 @@
         <v>0.26838563360762802</v>
       </c>
     </row>
-    <row r="75" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A75" s="1" t="s">
         <v>331</v>
       </c>
@@ -12316,7 +13880,7 @@
         <v>0.26226006746867903</v>
       </c>
     </row>
-    <row r="76" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A76" s="1" t="s">
         <v>332</v>
       </c>
@@ -12327,7 +13891,7 @@
         <v>0.26283415625491802</v>
       </c>
     </row>
-    <row r="77" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A77" s="1" t="s">
         <v>333</v>
       </c>
@@ -12338,7 +13902,7 @@
         <v>0.265891536409124</v>
       </c>
     </row>
-    <row r="78" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A78" s="1" t="s">
         <v>334</v>
       </c>
@@ -12349,7 +13913,7 @@
         <v>0.26086999753535101</v>
       </c>
     </row>
-    <row r="79" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A79" s="1" t="s">
         <v>335</v>
       </c>
@@ -12360,7 +13924,7 @@
         <v>0.264030412441006</v>
       </c>
     </row>
-    <row r="80" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A80" s="1" t="s">
         <v>336</v>
       </c>
@@ -12371,7 +13935,7 @@
         <v>0.26104421609513101</v>
       </c>
     </row>
-    <row r="81" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A81" s="1" t="s">
         <v>337</v>
       </c>
@@ -12382,7 +13946,7 @@
         <v>0.26790761730572898</v>
       </c>
     </row>
-    <row r="82" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A82" s="1" t="s">
         <v>338</v>
       </c>
@@ -12393,7 +13957,7 @@
         <v>0.26200964452208297</v>
       </c>
     </row>
-    <row r="83" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A83" s="1" t="s">
         <v>339</v>
       </c>
@@ -12404,7 +13968,7 @@
         <v>0.26657014430711701</v>
       </c>
     </row>
-    <row r="84" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A84" s="1" t="s">
         <v>340</v>
       </c>
@@ -12415,7 +13979,7 @@
         <v>0.264335730958146</v>
       </c>
     </row>
-    <row r="85" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A85" s="1" t="s">
         <v>341</v>
       </c>
@@ -12426,7 +13990,7 @@
         <v>0.26876048744697101</v>
       </c>
     </row>
-    <row r="86" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A86" s="1" t="s">
         <v>342</v>
       </c>
@@ -12437,7 +14001,7 @@
         <v>0.26514897700620299</v>
       </c>
     </row>
-    <row r="87" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A87" s="1" t="s">
         <v>343</v>
       </c>
@@ -12448,7 +14012,7 @@
         <v>0.26219390887345601</v>
       </c>
     </row>
-    <row r="88" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A88" s="1" t="s">
         <v>344</v>
       </c>
@@ -12459,7 +14023,7 @@
         <v>0.26184487099436499</v>
       </c>
     </row>
-    <row r="89" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A89" s="1" t="s">
         <v>345</v>
       </c>
@@ -12470,7 +14034,7 @@
         <v>0.26409583467590397</v>
       </c>
     </row>
-    <row r="90" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A90" s="1" t="s">
         <v>346</v>
       </c>
@@ -12481,7 +14045,7 @@
         <v>0.26424448419416702</v>
       </c>
     </row>
-    <row r="91" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A91" s="1" t="s">
         <v>347</v>
       </c>
@@ -12492,7 +14056,7 @@
         <v>0.26363414452799</v>
       </c>
     </row>
-    <row r="92" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A92" s="1" t="s">
         <v>348</v>
       </c>
@@ -12503,7 +14067,7 @@
         <v>0.26464837628465498</v>
       </c>
     </row>
-    <row r="93" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A93" s="1" t="s">
         <v>349</v>
       </c>
@@ -12514,7 +14078,7 @@
         <v>0.27030866825799199</v>
       </c>
     </row>
-    <row r="94" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A94" s="1" t="s">
         <v>350</v>
       </c>
@@ -12525,7 +14089,7 @@
         <v>0.23820566920665201</v>
       </c>
     </row>
-    <row r="95" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A95" s="1" t="s">
         <v>351</v>
       </c>
@@ -12536,7 +14100,7 @@
         <v>0.23716854436609899</v>
       </c>
     </row>
-    <row r="96" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A96" s="1" t="s">
         <v>352</v>
       </c>
@@ -12547,7 +14111,7 @@
         <v>0.24334889035587701</v>
       </c>
     </row>
-    <row r="97" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A97" s="1" t="s">
         <v>353</v>
       </c>
@@ -12558,7 +14122,7 @@
         <v>0.24139693907330401</v>
       </c>
     </row>
-    <row r="98" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A98" s="1" t="s">
         <v>354</v>
       </c>
@@ -12569,7 +14133,7 @@
         <v>0.24177140642297701</v>
       </c>
     </row>
-    <row r="99" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A99" s="1" t="s">
         <v>355</v>
       </c>
@@ -12580,7 +14144,7 @@
         <v>0.24611015618375001</v>
       </c>
     </row>
-    <row r="100" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A100" s="1" t="s">
         <v>356</v>
       </c>
@@ -12591,7 +14155,7 @@
         <v>0.24482638982888399</v>
       </c>
     </row>
-    <row r="101" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A101" s="1" t="s">
         <v>357</v>
       </c>
@@ -12602,7 +14166,7 @@
         <v>0.24047022478348701</v>
       </c>
     </row>
-    <row r="102" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A102" s="1" t="s">
         <v>358</v>
       </c>
@@ -12613,7 +14177,7 @@
         <v>0.24076714972723101</v>
       </c>
     </row>
-    <row r="103" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A103" s="1" t="s">
         <v>359</v>
       </c>
@@ -12624,7 +14188,7 @@
         <v>0.244370206125226</v>
       </c>
     </row>
-    <row r="104" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A104" s="1" t="s">
         <v>360</v>
       </c>
@@ -12635,7 +14199,7 @@
         <v>0.24313993631303599</v>
       </c>
     </row>
-    <row r="105" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A105" s="1" t="s">
         <v>361</v>
       </c>
@@ -12646,7 +14210,7 @@
         <v>0.240076934656237</v>
       </c>
     </row>
-    <row r="106" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A106" s="1" t="s">
         <v>362</v>
       </c>
@@ -12657,7 +14221,7 @@
         <v>0.242245334794052</v>
       </c>
     </row>
-    <row r="107" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A107" s="1" t="s">
         <v>363</v>
       </c>
@@ -12668,7 +14232,7 @@
         <v>0.24081642222489599</v>
       </c>
     </row>
-    <row r="108" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A108" s="1" t="s">
         <v>364</v>
       </c>
@@ -12679,7 +14243,7 @@
         <v>0.23946128860629701</v>
       </c>
     </row>
-    <row r="109" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A109" s="1" t="s">
         <v>365</v>
       </c>
@@ -12690,7 +14254,7 @@
         <v>0.24067136591591201</v>
       </c>
     </row>
-    <row r="110" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A110" s="1" t="s">
         <v>366</v>
       </c>
@@ -12701,7 +14265,7 @@
         <v>0.241804540636641</v>
       </c>
     </row>
-    <row r="111" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A111" s="1" t="s">
         <v>367</v>
       </c>
@@ -12712,7 +14276,7 @@
         <v>0.237876942608618</v>
       </c>
     </row>
-    <row r="112" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A112" s="1" t="s">
         <v>368</v>
       </c>
@@ -12723,7 +14287,7 @@
         <v>0.241838145831969</v>
       </c>
     </row>
-    <row r="113" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A113" s="1" t="s">
         <v>369</v>
       </c>
@@ -12734,7 +14298,7 @@
         <v>0.24402502768845699</v>
       </c>
     </row>
-    <row r="114" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A114" s="1" t="s">
         <v>370</v>
       </c>
@@ -12745,7 +14309,7 @@
         <v>0.23989744417664499</v>
       </c>
     </row>
-    <row r="115" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A115" s="1" t="s">
         <v>371</v>
       </c>
@@ -12756,7 +14320,7 @@
         <v>0.240176182150968</v>
       </c>
     </row>
-    <row r="116" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A116" s="1" t="s">
         <v>372</v>
       </c>
@@ -12767,7 +14331,7 @@
         <v>0.238939795428251</v>
       </c>
     </row>
-    <row r="117" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A117" s="1" t="s">
         <v>373</v>
       </c>
@@ -12778,7 +14342,7 @@
         <v>0.23962573892411401</v>
       </c>
     </row>
-    <row r="118" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A118" s="1" t="s">
         <v>374</v>
       </c>
@@ -12789,7 +14353,7 @@
         <v>0.24176111907040099</v>
       </c>
     </row>
-    <row r="119" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A119" s="1" t="s">
         <v>375</v>
       </c>
@@ -12800,7 +14364,7 @@
         <v>0.24348653683848701</v>
       </c>
     </row>
-    <row r="120" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A120" s="1" t="s">
         <v>376</v>
       </c>
@@ -12811,7 +14375,7 @@
         <v>0.24073031648363399</v>
       </c>
     </row>
-    <row r="121" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A121" s="1" t="s">
         <v>377</v>
       </c>
@@ -12822,7 +14386,7 @@
         <v>0.24558776594854301</v>
       </c>
     </row>
-    <row r="122" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A122" s="1" t="s">
         <v>378</v>
       </c>
@@ -12833,7 +14397,7 @@
         <v>0.239185337596831</v>
       </c>
     </row>
-    <row r="123" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A123" s="1" t="s">
         <v>379</v>
       </c>
@@ -12844,7 +14408,7 @@
         <v>0.241717931493385</v>
       </c>
     </row>
-    <row r="124" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A124" s="1" t="s">
         <v>380</v>
       </c>
@@ -12855,7 +14419,7 @@
         <v>0.24138266998260599</v>
       </c>
     </row>
-    <row r="125" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A125" s="1" t="s">
         <v>381</v>
       </c>
@@ -12875,7 +14439,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B2C84813-6F9B-41AD-8444-3DA3A143264B}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -12885,9 +14449,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5041D50F-BA36-4424-BB3F-938894C20C29}">
   <dimension ref="B1:D17"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <sheetData>
-    <row r="1" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:4" x14ac:dyDescent="0.55000000000000004">
       <c r="B1" t="s">
         <v>382</v>
       </c>
@@ -12895,7 +14459,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="2" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:4" x14ac:dyDescent="0.55000000000000004">
       <c r="B2" s="3">
         <v>46184</v>
       </c>
@@ -12903,7 +14467,7 @@
         <v>46164</v>
       </c>
     </row>
-    <row r="3" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:4" x14ac:dyDescent="0.55000000000000004">
       <c r="B3" s="4">
         <v>46183</v>
       </c>
@@ -12911,7 +14475,7 @@
         <v>46171</v>
       </c>
     </row>
-    <row r="4" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:4" x14ac:dyDescent="0.55000000000000004">
       <c r="B4" s="3">
         <v>46182</v>
       </c>
@@ -12919,7 +14483,7 @@
         <v>46199</v>
       </c>
     </row>
-    <row r="5" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:4" x14ac:dyDescent="0.55000000000000004">
       <c r="B5" s="3">
         <v>46178</v>
       </c>
@@ -12927,7 +14491,7 @@
         <v>46203</v>
       </c>
     </row>
-    <row r="6" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:4" x14ac:dyDescent="0.55000000000000004">
       <c r="B6" s="4">
         <v>46182</v>
       </c>
@@ -12935,7 +14499,7 @@
         <v>46202</v>
       </c>
     </row>
-    <row r="7" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:4" x14ac:dyDescent="0.55000000000000004">
       <c r="B7" s="4">
         <v>46178</v>
       </c>
@@ -12943,7 +14507,7 @@
         <v>46170</v>
       </c>
     </row>
-    <row r="8" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:4" x14ac:dyDescent="0.55000000000000004">
       <c r="B8" s="3">
         <v>46182</v>
       </c>
@@ -12951,47 +14515,47 @@
         <v>46210</v>
       </c>
     </row>
-    <row r="9" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:4" x14ac:dyDescent="0.55000000000000004">
       <c r="B9" s="3">
         <v>46178</v>
       </c>
     </row>
-    <row r="10" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:4" x14ac:dyDescent="0.55000000000000004">
       <c r="B10" s="4">
         <v>46190</v>
       </c>
     </row>
-    <row r="11" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:4" x14ac:dyDescent="0.55000000000000004">
       <c r="B11" s="4">
         <v>46191</v>
       </c>
     </row>
-    <row r="12" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:4" x14ac:dyDescent="0.55000000000000004">
       <c r="B12" s="3">
         <v>46204</v>
       </c>
     </row>
-    <row r="13" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:4" x14ac:dyDescent="0.55000000000000004">
       <c r="B13" s="4">
         <v>46185</v>
       </c>
     </row>
-    <row r="14" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:4" x14ac:dyDescent="0.55000000000000004">
       <c r="B14" s="3">
         <v>46205</v>
       </c>
     </row>
-    <row r="15" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:4" x14ac:dyDescent="0.55000000000000004">
       <c r="B15" s="4">
         <v>46188</v>
       </c>
     </row>
-    <row r="16" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:4" x14ac:dyDescent="0.55000000000000004">
       <c r="B16" s="4">
         <v>46189</v>
       </c>
     </row>
-    <row r="17" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:4" x14ac:dyDescent="0.55000000000000004">
       <c r="B17" s="3">
         <v>46209</v>
       </c>

--- a/Fit Results/Together.xlsx
+++ b/Fit Results/Together.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Diego\git\6s7p\Fit Results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8140C56-2404-4BC5-8886-65A21B0A48D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF4CA369-446C-4A68-9325-CA745075709C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1555,105 +1555,105 @@
           </c:trendline>
           <c:xVal>
             <c:numRef>
-              <c:f>'F1=3'!$B$2:$B$272</c:f>
+              <c:f>'F1=3'!$B$2:$B$269</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="271"/>
+                <c:ptCount val="268"/>
                 <c:pt idx="0">
+                  <c:v>8.2927304597387206</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>8.2237273067390202</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>8.26640584418465</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>8.2614937671479094</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>8.1948628050432095</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>8.1304154901890406</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>8.2121360213246692</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>8.2898703177931896</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>8.3727208112640206</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>8.4368095561837997</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>8.4364141305933895</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>8.4084015562695207</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>8.5099572412062301</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>8.4321434520724008</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>8.4721216638779193</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>8.4953666075608503</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>8.5996727461700306</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>8.6033820921791602</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>8.4545546426380405</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>8.5889106546587897</c:v>
+                </c:pt>
+                <c:pt idx="20">
                   <c:v>8.5895120122534792</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="21">
                   <c:v>8.6524212475503699</c:v>
                 </c:pt>
-                <c:pt idx="2">
-                  <c:v>8.2927304597387206</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>8.4368095561837997</c:v>
-                </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="22">
                   <c:v>8.6554109919161206</c:v>
                 </c:pt>
-                <c:pt idx="5">
-                  <c:v>8.2237273067390202</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>8.26640584418465</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>8.2614937671479094</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>8.1948628050432095</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>8.1304154901890406</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>8.2121360213246692</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>8.2898703177931896</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>8.3727208112640206</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>8.4364141305933895</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>8.4084015562695207</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>8.5099572412062301</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>8.4321434520724008</c:v>
-                </c:pt>
-                <c:pt idx="17">
+                <c:pt idx="23">
                   <c:v>8.53551089338964</c:v>
                 </c:pt>
-                <c:pt idx="18">
-                  <c:v>8.4721216638779193</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>8.4953666075608503</c:v>
-                </c:pt>
-                <c:pt idx="20">
+                <c:pt idx="24">
                   <c:v>8.7711252103094601</c:v>
                 </c:pt>
-                <c:pt idx="21">
-                  <c:v>8.5996727461700306</c:v>
-                </c:pt>
-                <c:pt idx="22">
+                <c:pt idx="25">
                   <c:v>8.5801266895029205</c:v>
                 </c:pt>
-                <c:pt idx="23">
+                <c:pt idx="26">
                   <c:v>8.5783681642005494</c:v>
                 </c:pt>
-                <c:pt idx="24">
+                <c:pt idx="27">
                   <c:v>8.6129268121772302</c:v>
                 </c:pt>
-                <c:pt idx="25">
+                <c:pt idx="28">
                   <c:v>8.6349505815443095</c:v>
                 </c:pt>
-                <c:pt idx="26">
+                <c:pt idx="29">
                   <c:v>8.5827352500219707</c:v>
                 </c:pt>
-                <c:pt idx="27">
-                  <c:v>8.6033820921791602</c:v>
-                </c:pt>
-                <c:pt idx="28">
+                <c:pt idx="30">
                   <c:v>8.6784045244654298</c:v>
                 </c:pt>
-                <c:pt idx="29">
+                <c:pt idx="31">
                   <c:v>8.6432150051153496</c:v>
-                </c:pt>
-                <c:pt idx="30">
-                  <c:v>8.4545546426380405</c:v>
-                </c:pt>
-                <c:pt idx="31">
-                  <c:v>8.5889106546587897</c:v>
                 </c:pt>
                 <c:pt idx="32">
                   <c:v>7.0733851626533504</c:v>
@@ -2186,181 +2186,181 @@
                 <c:pt idx="208">
                   <c:v>10.5903781690852</c:v>
                 </c:pt>
+                <c:pt idx="209">
+                  <c:v>13.2697393001639</c:v>
+                </c:pt>
+                <c:pt idx="210">
+                  <c:v>13.085484930856</c:v>
+                </c:pt>
+                <c:pt idx="211">
+                  <c:v>13.175945695541801</c:v>
+                </c:pt>
                 <c:pt idx="212">
-                  <c:v>13.2697393001639</c:v>
+                  <c:v>12.932688227182499</c:v>
                 </c:pt>
                 <c:pt idx="213">
-                  <c:v>13.085484930856</c:v>
+                  <c:v>12.983441137506301</c:v>
                 </c:pt>
                 <c:pt idx="214">
-                  <c:v>13.175945695541801</c:v>
+                  <c:v>13.0765465639323</c:v>
                 </c:pt>
                 <c:pt idx="215">
-                  <c:v>12.932688227182499</c:v>
+                  <c:v>13.1139776982864</c:v>
                 </c:pt>
                 <c:pt idx="216">
-                  <c:v>12.983441137506301</c:v>
+                  <c:v>13.148082507003</c:v>
                 </c:pt>
                 <c:pt idx="217">
-                  <c:v>13.0765465639323</c:v>
+                  <c:v>12.9457941612001</c:v>
                 </c:pt>
                 <c:pt idx="218">
-                  <c:v>13.1139776982864</c:v>
+                  <c:v>13.0137021255065</c:v>
                 </c:pt>
                 <c:pt idx="219">
-                  <c:v>13.148082507003</c:v>
+                  <c:v>13.1418022843663</c:v>
                 </c:pt>
                 <c:pt idx="220">
-                  <c:v>12.9457941612001</c:v>
+                  <c:v>13.1707068509</c:v>
                 </c:pt>
                 <c:pt idx="221">
-                  <c:v>13.0137021255065</c:v>
+                  <c:v>13.2066468551924</c:v>
                 </c:pt>
                 <c:pt idx="222">
-                  <c:v>13.1418022843663</c:v>
+                  <c:v>13.158519557395699</c:v>
                 </c:pt>
                 <c:pt idx="223">
-                  <c:v>13.1707068509</c:v>
+                  <c:v>13.101689684028599</c:v>
                 </c:pt>
                 <c:pt idx="224">
-                  <c:v>13.2066468551924</c:v>
+                  <c:v>13.214174220163899</c:v>
                 </c:pt>
                 <c:pt idx="225">
-                  <c:v>13.158519557395699</c:v>
+                  <c:v>13.1096701956908</c:v>
                 </c:pt>
                 <c:pt idx="226">
-                  <c:v>13.101689684028599</c:v>
+                  <c:v>13.073395646730701</c:v>
                 </c:pt>
                 <c:pt idx="227">
-                  <c:v>13.214174220163899</c:v>
+                  <c:v>13.312833843466599</c:v>
                 </c:pt>
                 <c:pt idx="228">
-                  <c:v>13.1096701956908</c:v>
+                  <c:v>13.124987483828299</c:v>
                 </c:pt>
                 <c:pt idx="229">
-                  <c:v>13.073395646730701</c:v>
+                  <c:v>12.978247315348099</c:v>
                 </c:pt>
                 <c:pt idx="230">
-                  <c:v>13.312833843466599</c:v>
+                  <c:v>13.0256010563036</c:v>
                 </c:pt>
                 <c:pt idx="231">
-                  <c:v>13.124987483828299</c:v>
+                  <c:v>12.962310430945999</c:v>
                 </c:pt>
                 <c:pt idx="232">
-                  <c:v>12.978247315348099</c:v>
+                  <c:v>13.003649574191501</c:v>
                 </c:pt>
                 <c:pt idx="233">
-                  <c:v>13.0256010563036</c:v>
+                  <c:v>13.0669427926527</c:v>
                 </c:pt>
                 <c:pt idx="234">
-                  <c:v>12.962310430945999</c:v>
+                  <c:v>13.118146624426201</c:v>
                 </c:pt>
                 <c:pt idx="235">
-                  <c:v>13.003649574191501</c:v>
+                  <c:v>13.061519052065201</c:v>
                 </c:pt>
                 <c:pt idx="236">
-                  <c:v>13.0669427926527</c:v>
+                  <c:v>13.0135879028039</c:v>
                 </c:pt>
                 <c:pt idx="237">
-                  <c:v>13.118146624426201</c:v>
+                  <c:v>14.610387851091801</c:v>
                 </c:pt>
                 <c:pt idx="238">
-                  <c:v>13.061519052065201</c:v>
+                  <c:v>14.824645793302301</c:v>
                 </c:pt>
                 <c:pt idx="239">
-                  <c:v>13.0135879028039</c:v>
+                  <c:v>14.4528707103913</c:v>
                 </c:pt>
                 <c:pt idx="240">
-                  <c:v>14.610387851091801</c:v>
+                  <c:v>14.6109532885724</c:v>
                 </c:pt>
                 <c:pt idx="241">
-                  <c:v>14.824645793302301</c:v>
+                  <c:v>14.525535608882601</c:v>
                 </c:pt>
                 <c:pt idx="242">
-                  <c:v>14.4528707103913</c:v>
+                  <c:v>14.703570164436799</c:v>
                 </c:pt>
                 <c:pt idx="243">
-                  <c:v>14.6109532885724</c:v>
+                  <c:v>14.6469605754983</c:v>
                 </c:pt>
                 <c:pt idx="244">
-                  <c:v>14.525535608882601</c:v>
+                  <c:v>14.4430203101595</c:v>
                 </c:pt>
                 <c:pt idx="245">
-                  <c:v>14.703570164436799</c:v>
+                  <c:v>14.549598435905899</c:v>
                 </c:pt>
                 <c:pt idx="246">
-                  <c:v>14.6469605754983</c:v>
+                  <c:v>14.7043335718615</c:v>
                 </c:pt>
                 <c:pt idx="247">
-                  <c:v>14.4430203101595</c:v>
+                  <c:v>14.770828981153199</c:v>
                 </c:pt>
                 <c:pt idx="248">
-                  <c:v>14.549598435905899</c:v>
+                  <c:v>14.7903674498711</c:v>
                 </c:pt>
                 <c:pt idx="249">
-                  <c:v>14.7043335718615</c:v>
+                  <c:v>14.6129136258226</c:v>
                 </c:pt>
                 <c:pt idx="250">
-                  <c:v>14.770828981153199</c:v>
+                  <c:v>14.5285253520751</c:v>
                 </c:pt>
                 <c:pt idx="251">
-                  <c:v>14.7903674498711</c:v>
+                  <c:v>14.4495865267067</c:v>
                 </c:pt>
                 <c:pt idx="252">
-                  <c:v>14.6129136258226</c:v>
+                  <c:v>14.524765784844201</c:v>
                 </c:pt>
                 <c:pt idx="253">
-                  <c:v>14.5285253520751</c:v>
+                  <c:v>14.764112552014099</c:v>
                 </c:pt>
                 <c:pt idx="254">
-                  <c:v>14.4495865267067</c:v>
+                  <c:v>14.7106184874969</c:v>
                 </c:pt>
                 <c:pt idx="255">
-                  <c:v>14.524765784844201</c:v>
+                  <c:v>14.749177714501</c:v>
                 </c:pt>
                 <c:pt idx="256">
-                  <c:v>14.764112552014099</c:v>
+                  <c:v>14.6684970880551</c:v>
                 </c:pt>
                 <c:pt idx="257">
-                  <c:v>14.7106184874969</c:v>
+                  <c:v>14.5764121579489</c:v>
                 </c:pt>
                 <c:pt idx="258">
-                  <c:v>14.749177714501</c:v>
+                  <c:v>14.633716179029699</c:v>
                 </c:pt>
                 <c:pt idx="259">
-                  <c:v>14.6684970880551</c:v>
+                  <c:v>14.618198212113001</c:v>
                 </c:pt>
                 <c:pt idx="260">
-                  <c:v>14.5764121579489</c:v>
+                  <c:v>14.482642723981799</c:v>
                 </c:pt>
                 <c:pt idx="261">
-                  <c:v>14.633716179029699</c:v>
+                  <c:v>14.491750683935599</c:v>
                 </c:pt>
                 <c:pt idx="262">
-                  <c:v>14.618198212113001</c:v>
+                  <c:v>17.825013007136501</c:v>
                 </c:pt>
                 <c:pt idx="263">
-                  <c:v>14.482642723981799</c:v>
+                  <c:v>17.9319730766783</c:v>
                 </c:pt>
                 <c:pt idx="264">
-                  <c:v>14.491750683935599</c:v>
+                  <c:v>18.039044650769</c:v>
                 </c:pt>
                 <c:pt idx="265">
-                  <c:v>17.825013007136501</c:v>
+                  <c:v>18.0604756933053</c:v>
                 </c:pt>
                 <c:pt idx="266">
-                  <c:v>17.9319730766783</c:v>
+                  <c:v>17.9979172106978</c:v>
                 </c:pt>
                 <c:pt idx="267">
-                  <c:v>18.039044650769</c:v>
-                </c:pt>
-                <c:pt idx="268">
-                  <c:v>18.0604756933053</c:v>
-                </c:pt>
-                <c:pt idx="269">
-                  <c:v>17.9979172106978</c:v>
-                </c:pt>
-                <c:pt idx="270">
                   <c:v>17.998827423434999</c:v>
                 </c:pt>
               </c:numCache>
@@ -2368,105 +2368,105 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'F1=3'!$C$2:$C$272</c:f>
+              <c:f>'F1=3'!$C$2:$C$269</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="271"/>
+                <c:ptCount val="268"/>
                 <c:pt idx="0">
+                  <c:v>0.13879302222888601</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.13688104388401501</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.135835488526413</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.13460037386162699</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.133457625743262</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.13379913857126899</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.135112188890431</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.130316004197812</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.13498234565869699</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.14134057599559999</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.13854180631109</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.13743837454275501</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.13738267695902801</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0.14159428045373601</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.14391242117178599</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0.13920272125085101</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0.13915991329959099</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0.13928443937518301</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0.14380448214622399</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>0.13910873933717599</c:v>
+                </c:pt>
+                <c:pt idx="20">
                   <c:v>0.14198189433295499</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="21">
                   <c:v>0.14200693706074399</c:v>
                 </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.13879302222888601</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.14134057599559999</c:v>
-                </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="22">
                   <c:v>0.14287369952523299</c:v>
                 </c:pt>
-                <c:pt idx="5">
-                  <c:v>0.13688104388401501</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>0.135835488526413</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>0.13460037386162699</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>0.133457625743262</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>0.13379913857126899</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>0.135112188890431</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>0.130316004197812</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>0.13498234565869699</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>0.13854180631109</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>0.13743837454275501</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>0.13738267695902801</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>0.14159428045373601</c:v>
-                </c:pt>
-                <c:pt idx="17">
+                <c:pt idx="23">
                   <c:v>0.14232784705226301</c:v>
                 </c:pt>
-                <c:pt idx="18">
-                  <c:v>0.14391242117178599</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>0.13920272125085101</c:v>
-                </c:pt>
-                <c:pt idx="20">
+                <c:pt idx="24">
                   <c:v>0.14459533841685501</c:v>
                 </c:pt>
-                <c:pt idx="21">
-                  <c:v>0.13915991329959099</c:v>
-                </c:pt>
-                <c:pt idx="22">
+                <c:pt idx="25">
                   <c:v>0.144975058104169</c:v>
                 </c:pt>
-                <c:pt idx="23">
+                <c:pt idx="26">
                   <c:v>0.14496624110967199</c:v>
                 </c:pt>
-                <c:pt idx="24">
+                <c:pt idx="27">
                   <c:v>0.14341121488491801</c:v>
                 </c:pt>
-                <c:pt idx="25">
+                <c:pt idx="28">
                   <c:v>0.14388771373763901</c:v>
                 </c:pt>
-                <c:pt idx="26">
+                <c:pt idx="29">
                   <c:v>0.14091026017191899</c:v>
                 </c:pt>
-                <c:pt idx="27">
-                  <c:v>0.13928443937518301</c:v>
-                </c:pt>
-                <c:pt idx="28">
+                <c:pt idx="30">
                   <c:v>0.14449758570660601</c:v>
                 </c:pt>
-                <c:pt idx="29">
+                <c:pt idx="31">
                   <c:v>0.14272080636913501</c:v>
-                </c:pt>
-                <c:pt idx="30">
-                  <c:v>0.14380448214622399</c:v>
-                </c:pt>
-                <c:pt idx="31">
-                  <c:v>0.13910873933717599</c:v>
                 </c:pt>
                 <c:pt idx="32">
                   <c:v>0.117218052017694</c:v>
@@ -2999,181 +2999,181 @@
                 <c:pt idx="208">
                   <c:v>0.17654554655181801</c:v>
                 </c:pt>
+                <c:pt idx="209">
+                  <c:v>0.21689563024651701</c:v>
+                </c:pt>
+                <c:pt idx="210">
+                  <c:v>0.21250705902688999</c:v>
+                </c:pt>
+                <c:pt idx="211">
+                  <c:v>0.21268324019514501</c:v>
+                </c:pt>
                 <c:pt idx="212">
-                  <c:v>0.21689563024651701</c:v>
+                  <c:v>0.21049345542616399</c:v>
                 </c:pt>
                 <c:pt idx="213">
-                  <c:v>0.21250705902688999</c:v>
+                  <c:v>0.214431740824571</c:v>
                 </c:pt>
                 <c:pt idx="214">
-                  <c:v>0.21268324019514501</c:v>
+                  <c:v>0.21026943516751501</c:v>
                 </c:pt>
                 <c:pt idx="215">
-                  <c:v>0.21049345542616399</c:v>
+                  <c:v>0.211983108185162</c:v>
                 </c:pt>
                 <c:pt idx="216">
-                  <c:v>0.214431740824571</c:v>
+                  <c:v>0.212540414406241</c:v>
                 </c:pt>
                 <c:pt idx="217">
-                  <c:v>0.21026943516751501</c:v>
+                  <c:v>0.21316933311979799</c:v>
                 </c:pt>
                 <c:pt idx="218">
-                  <c:v>0.211983108185162</c:v>
+                  <c:v>0.212515123863107</c:v>
                 </c:pt>
                 <c:pt idx="219">
-                  <c:v>0.212540414406241</c:v>
+                  <c:v>0.21030240285409901</c:v>
                 </c:pt>
                 <c:pt idx="220">
-                  <c:v>0.21316933311979799</c:v>
+                  <c:v>0.213000429148374</c:v>
                 </c:pt>
                 <c:pt idx="221">
-                  <c:v>0.212515123863107</c:v>
+                  <c:v>0.21204120218539499</c:v>
                 </c:pt>
                 <c:pt idx="222">
-                  <c:v>0.21030240285409901</c:v>
+                  <c:v>0.211005527878392</c:v>
                 </c:pt>
                 <c:pt idx="223">
-                  <c:v>0.213000429148374</c:v>
+                  <c:v>0.21490935202097999</c:v>
                 </c:pt>
                 <c:pt idx="224">
-                  <c:v>0.21204120218539499</c:v>
+                  <c:v>0.214705500945685</c:v>
                 </c:pt>
                 <c:pt idx="225">
-                  <c:v>0.211005527878392</c:v>
+                  <c:v>0.21046954774395399</c:v>
                 </c:pt>
                 <c:pt idx="226">
-                  <c:v>0.21490935202097999</c:v>
+                  <c:v>0.212979730482002</c:v>
                 </c:pt>
                 <c:pt idx="227">
-                  <c:v>0.214705500945685</c:v>
+                  <c:v>0.21145441547031901</c:v>
                 </c:pt>
                 <c:pt idx="228">
-                  <c:v>0.21046954774395399</c:v>
+                  <c:v>0.21334229216903</c:v>
                 </c:pt>
                 <c:pt idx="229">
-                  <c:v>0.212979730482002</c:v>
+                  <c:v>0.21313225436689001</c:v>
                 </c:pt>
                 <c:pt idx="230">
-                  <c:v>0.21145441547031901</c:v>
+                  <c:v>0.21364986681269199</c:v>
                 </c:pt>
                 <c:pt idx="231">
-                  <c:v>0.21334229216903</c:v>
+                  <c:v>0.21046298569896901</c:v>
                 </c:pt>
                 <c:pt idx="232">
-                  <c:v>0.21313225436689001</c:v>
+                  <c:v>0.21370475343700501</c:v>
                 </c:pt>
                 <c:pt idx="233">
-                  <c:v>0.21364986681269199</c:v>
+                  <c:v>0.213427613164866</c:v>
                 </c:pt>
                 <c:pt idx="234">
-                  <c:v>0.21046298569896901</c:v>
+                  <c:v>0.21285885222227299</c:v>
                 </c:pt>
                 <c:pt idx="235">
-                  <c:v>0.21370475343700501</c:v>
+                  <c:v>0.21229610722325801</c:v>
                 </c:pt>
                 <c:pt idx="236">
-                  <c:v>0.213427613164866</c:v>
+                  <c:v>0.213479995323273</c:v>
                 </c:pt>
                 <c:pt idx="237">
-                  <c:v>0.21285885222227299</c:v>
+                  <c:v>0.23747635372092801</c:v>
                 </c:pt>
                 <c:pt idx="238">
-                  <c:v>0.21229610722325801</c:v>
+                  <c:v>0.24180291421483799</c:v>
                 </c:pt>
                 <c:pt idx="239">
-                  <c:v>0.213479995323273</c:v>
+                  <c:v>0.23775144209915899</c:v>
                 </c:pt>
                 <c:pt idx="240">
-                  <c:v>0.23747635372092801</c:v>
+                  <c:v>0.24065215342237201</c:v>
                 </c:pt>
                 <c:pt idx="241">
-                  <c:v>0.24180291421483799</c:v>
+                  <c:v>0.238634580986853</c:v>
                 </c:pt>
                 <c:pt idx="242">
-                  <c:v>0.23775144209915899</c:v>
+                  <c:v>0.24123516367901099</c:v>
                 </c:pt>
                 <c:pt idx="243">
-                  <c:v>0.24065215342237201</c:v>
+                  <c:v>0.23838761262462899</c:v>
                 </c:pt>
                 <c:pt idx="244">
-                  <c:v>0.238634580986853</c:v>
+                  <c:v>0.23787175668006799</c:v>
                 </c:pt>
                 <c:pt idx="245">
-                  <c:v>0.24123516367901099</c:v>
+                  <c:v>0.235957408677299</c:v>
                 </c:pt>
                 <c:pt idx="246">
-                  <c:v>0.23838761262462899</c:v>
+                  <c:v>0.23761103430247099</c:v>
                 </c:pt>
                 <c:pt idx="247">
-                  <c:v>0.23787175668006799</c:v>
+                  <c:v>0.24049928819975</c:v>
                 </c:pt>
                 <c:pt idx="248">
-                  <c:v>0.235957408677299</c:v>
+                  <c:v>0.23875237313230799</c:v>
                 </c:pt>
                 <c:pt idx="249">
-                  <c:v>0.23761103430247099</c:v>
+                  <c:v>0.23577509684512599</c:v>
                 </c:pt>
                 <c:pt idx="250">
-                  <c:v>0.24049928819975</c:v>
+                  <c:v>0.23798590162913699</c:v>
                 </c:pt>
                 <c:pt idx="251">
-                  <c:v>0.23875237313230799</c:v>
+                  <c:v>0.23776270729380899</c:v>
                 </c:pt>
                 <c:pt idx="252">
-                  <c:v>0.23577509684512599</c:v>
+                  <c:v>0.23525871098023601</c:v>
                 </c:pt>
                 <c:pt idx="253">
-                  <c:v>0.23798590162913699</c:v>
+                  <c:v>0.23822698567085801</c:v>
                 </c:pt>
                 <c:pt idx="254">
-                  <c:v>0.23776270729380899</c:v>
+                  <c:v>0.236137249858582</c:v>
                 </c:pt>
                 <c:pt idx="255">
-                  <c:v>0.23525871098023601</c:v>
+                  <c:v>0.236589149526167</c:v>
                 </c:pt>
                 <c:pt idx="256">
-                  <c:v>0.23822698567085801</c:v>
+                  <c:v>0.234995035195148</c:v>
                 </c:pt>
                 <c:pt idx="257">
-                  <c:v>0.236137249858582</c:v>
+                  <c:v>0.238435257488993</c:v>
                 </c:pt>
                 <c:pt idx="258">
-                  <c:v>0.236589149526167</c:v>
+                  <c:v>0.23631298859917599</c:v>
                 </c:pt>
                 <c:pt idx="259">
-                  <c:v>0.234995035195148</c:v>
+                  <c:v>0.238968925765909</c:v>
                 </c:pt>
                 <c:pt idx="260">
-                  <c:v>0.238435257488993</c:v>
+                  <c:v>0.237506075673066</c:v>
                 </c:pt>
                 <c:pt idx="261">
-                  <c:v>0.23631298859917599</c:v>
+                  <c:v>0.237718713583811</c:v>
                 </c:pt>
                 <c:pt idx="262">
-                  <c:v>0.238968925765909</c:v>
+                  <c:v>0.29193451692567801</c:v>
                 </c:pt>
                 <c:pt idx="263">
-                  <c:v>0.237506075673066</c:v>
+                  <c:v>0.28873287738484599</c:v>
                 </c:pt>
                 <c:pt idx="264">
-                  <c:v>0.237718713583811</c:v>
+                  <c:v>0.28985427653153101</c:v>
                 </c:pt>
                 <c:pt idx="265">
-                  <c:v>0.29193451692567801</c:v>
+                  <c:v>0.29473582812057803</c:v>
                 </c:pt>
                 <c:pt idx="266">
-                  <c:v>0.28873287738484599</c:v>
+                  <c:v>0.29630016894823502</c:v>
                 </c:pt>
                 <c:pt idx="267">
-                  <c:v>0.28985427653153101</c:v>
-                </c:pt>
-                <c:pt idx="268">
-                  <c:v>0.29473582812057803</c:v>
-                </c:pt>
-                <c:pt idx="269">
-                  <c:v>0.29630016894823502</c:v>
-                </c:pt>
-                <c:pt idx="270">
                   <c:v>0.290375757335809</c:v>
                 </c:pt>
               </c:numCache>
@@ -4470,100 +4470,100 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="209"/>
                 <c:pt idx="0">
+                  <c:v>8.2927304597387206</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>8.2237273067390202</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>8.26640584418465</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>8.2614937671479094</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>8.1948628050432095</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>8.1304154901890406</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>8.2121360213246692</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>8.2898703177931896</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>8.3727208112640206</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>8.4368095561837997</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>8.4364141305933895</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>8.4084015562695207</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>8.5099572412062301</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>8.4321434520724008</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>8.4721216638779193</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>8.4953666075608503</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>8.5996727461700306</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>8.6033820921791602</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>8.4545546426380405</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>8.5889106546587897</c:v>
+                </c:pt>
+                <c:pt idx="20">
                   <c:v>8.5895120122534792</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="21">
                   <c:v>8.6524212475503699</c:v>
                 </c:pt>
-                <c:pt idx="2">
-                  <c:v>8.2927304597387206</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>8.4368095561837997</c:v>
-                </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="22">
                   <c:v>8.6554109919161206</c:v>
                 </c:pt>
-                <c:pt idx="5">
-                  <c:v>8.2237273067390202</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>8.26640584418465</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>8.2614937671479094</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>8.1948628050432095</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>8.1304154901890406</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>8.2121360213246692</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>8.2898703177931896</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>8.3727208112640206</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>8.4364141305933895</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>8.4084015562695207</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>8.5099572412062301</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>8.4321434520724008</c:v>
-                </c:pt>
-                <c:pt idx="17">
+                <c:pt idx="23">
                   <c:v>8.53551089338964</c:v>
                 </c:pt>
-                <c:pt idx="18">
-                  <c:v>8.4721216638779193</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>8.4953666075608503</c:v>
-                </c:pt>
-                <c:pt idx="20">
+                <c:pt idx="24">
                   <c:v>8.7711252103094601</c:v>
                 </c:pt>
-                <c:pt idx="21">
-                  <c:v>8.5996727461700306</c:v>
-                </c:pt>
-                <c:pt idx="22">
+                <c:pt idx="25">
                   <c:v>8.5801266895029205</c:v>
                 </c:pt>
-                <c:pt idx="23">
+                <c:pt idx="26">
                   <c:v>8.5783681642005494</c:v>
                 </c:pt>
-                <c:pt idx="24">
+                <c:pt idx="27">
                   <c:v>8.6129268121772302</c:v>
                 </c:pt>
-                <c:pt idx="25">
+                <c:pt idx="28">
                   <c:v>8.6349505815443095</c:v>
                 </c:pt>
-                <c:pt idx="26">
+                <c:pt idx="29">
                   <c:v>8.5827352500219707</c:v>
                 </c:pt>
-                <c:pt idx="27">
-                  <c:v>8.6033820921791602</c:v>
-                </c:pt>
-                <c:pt idx="28">
+                <c:pt idx="30">
                   <c:v>8.6784045244654298</c:v>
                 </c:pt>
-                <c:pt idx="29">
+                <c:pt idx="31">
                   <c:v>8.6432150051153496</c:v>
-                </c:pt>
-                <c:pt idx="30">
-                  <c:v>8.4545546426380405</c:v>
-                </c:pt>
-                <c:pt idx="31">
-                  <c:v>8.5889106546587897</c:v>
                 </c:pt>
                 <c:pt idx="32">
                   <c:v>7.0733851626533504</c:v>
@@ -5106,100 +5106,100 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="209"/>
                 <c:pt idx="0">
+                  <c:v>0.13879302222888601</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.13688104388401501</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.135835488526413</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.13460037386162699</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.133457625743262</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.13379913857126899</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.135112188890431</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.130316004197812</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.13498234565869699</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.14134057599559999</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.13854180631109</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.13743837454275501</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.13738267695902801</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0.14159428045373601</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.14391242117178599</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0.13920272125085101</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0.13915991329959099</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0.13928443937518301</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0.14380448214622399</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>0.13910873933717599</c:v>
+                </c:pt>
+                <c:pt idx="20">
                   <c:v>0.14198189433295499</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="21">
                   <c:v>0.14200693706074399</c:v>
                 </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.13879302222888601</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.14134057599559999</c:v>
-                </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="22">
                   <c:v>0.14287369952523299</c:v>
                 </c:pt>
-                <c:pt idx="5">
-                  <c:v>0.13688104388401501</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>0.135835488526413</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>0.13460037386162699</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>0.133457625743262</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>0.13379913857126899</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>0.135112188890431</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>0.130316004197812</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>0.13498234565869699</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>0.13854180631109</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>0.13743837454275501</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>0.13738267695902801</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>0.14159428045373601</c:v>
-                </c:pt>
-                <c:pt idx="17">
+                <c:pt idx="23">
                   <c:v>0.14232784705226301</c:v>
                 </c:pt>
-                <c:pt idx="18">
-                  <c:v>0.14391242117178599</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>0.13920272125085101</c:v>
-                </c:pt>
-                <c:pt idx="20">
+                <c:pt idx="24">
                   <c:v>0.14459533841685501</c:v>
                 </c:pt>
-                <c:pt idx="21">
-                  <c:v>0.13915991329959099</c:v>
-                </c:pt>
-                <c:pt idx="22">
+                <c:pt idx="25">
                   <c:v>0.144975058104169</c:v>
                 </c:pt>
-                <c:pt idx="23">
+                <c:pt idx="26">
                   <c:v>0.14496624110967199</c:v>
                 </c:pt>
-                <c:pt idx="24">
+                <c:pt idx="27">
                   <c:v>0.14341121488491801</c:v>
                 </c:pt>
-                <c:pt idx="25">
+                <c:pt idx="28">
                   <c:v>0.14388771373763901</c:v>
                 </c:pt>
-                <c:pt idx="26">
+                <c:pt idx="29">
                   <c:v>0.14091026017191899</c:v>
                 </c:pt>
-                <c:pt idx="27">
-                  <c:v>0.13928443937518301</c:v>
-                </c:pt>
-                <c:pt idx="28">
+                <c:pt idx="30">
                   <c:v>0.14449758570660601</c:v>
                 </c:pt>
-                <c:pt idx="29">
+                <c:pt idx="31">
                   <c:v>0.14272080636913501</c:v>
-                </c:pt>
-                <c:pt idx="30">
-                  <c:v>0.14380448214622399</c:v>
-                </c:pt>
-                <c:pt idx="31">
-                  <c:v>0.13910873933717599</c:v>
                 </c:pt>
                 <c:pt idx="32">
                   <c:v>0.117218052017694</c:v>
@@ -8926,7 +8926,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H297"/>
+  <dimension ref="A1:H294"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="11.5703125" bestFit="1" customWidth="1"/>
@@ -8944,84 +8944,84 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2">
-        <v>8.5895120122534792</v>
-      </c>
-      <c r="C2">
-        <v>0.14198189433295499</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3">
-        <v>8.6524212475503699</v>
-      </c>
-      <c r="C3">
-        <v>0.14200693706074399</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+    <row r="2" spans="1:8" ht="45" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B4">
+      <c r="B2" s="1">
         <v>8.2927304597387206</v>
       </c>
-      <c r="C4">
+      <c r="C2" s="1">
         <v>0.13879302222888601</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5">
-        <v>8.4368095561837997</v>
-      </c>
-      <c r="C5">
-        <v>0.14134057599559999</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>7</v>
-      </c>
-      <c r="B6">
-        <v>8.6554109919161206</v>
-      </c>
-      <c r="C6">
-        <v>0.14287369952523299</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
+    <row r="3" spans="1:8" ht="45" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="B7">
+      <c r="B3" s="1">
         <v>8.2237273067390202</v>
       </c>
-      <c r="C7">
+      <c r="C3" s="1">
         <v>0.13688104388401501</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="45" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B4" s="1">
+        <v>8.26640584418465</v>
+      </c>
+      <c r="C4" s="1">
+        <v>0.135835488526413</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="45" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B5" s="1">
+        <v>8.2614937671479094</v>
+      </c>
+      <c r="C5" s="1">
+        <v>0.13460037386162699</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="45" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="B6" s="1">
+        <v>8.1948628050432095</v>
+      </c>
+      <c r="C6" s="1">
+        <v>0.133457625743262</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="45" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>419</v>
+      </c>
+      <c r="B7" s="1">
+        <v>8.1304154901890406</v>
+      </c>
+      <c r="C7" s="1">
+        <v>0.13379913857126899</v>
       </c>
       <c r="G7" t="s">
         <v>384</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="45" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>26</v>
-      </c>
-      <c r="B8">
-        <v>8.26640584418465</v>
-      </c>
-      <c r="C8">
-        <v>0.135835488526413</v>
+      <c r="A8" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8" s="1">
+        <v>8.2121360213246692</v>
+      </c>
+      <c r="C8" s="1">
+        <v>0.135112188890431</v>
       </c>
       <c r="F8" s="1" t="s">
         <v>5</v>
@@ -9034,14 +9034,14 @@
       </c>
     </row>
     <row r="9" spans="1:8" ht="45" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>27</v>
-      </c>
-      <c r="B9">
-        <v>8.2614937671479094</v>
-      </c>
-      <c r="C9">
-        <v>0.13460037386162699</v>
+      <c r="A9" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="B9" s="1">
+        <v>8.2898703177931896</v>
+      </c>
+      <c r="C9" s="1">
+        <v>0.130316004197812</v>
       </c>
       <c r="F9" s="1" t="s">
         <v>25</v>
@@ -9054,14 +9054,14 @@
       </c>
     </row>
     <row r="10" spans="1:8" ht="45" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>418</v>
-      </c>
-      <c r="B10">
-        <v>8.1948628050432095</v>
-      </c>
-      <c r="C10">
-        <v>0.133457625743262</v>
+      <c r="A10" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B10" s="1">
+        <v>8.3727208112640206</v>
+      </c>
+      <c r="C10" s="1">
+        <v>0.13498234565869699</v>
       </c>
       <c r="F10" s="1" t="s">
         <v>26</v>
@@ -9074,14 +9074,14 @@
       </c>
     </row>
     <row r="11" spans="1:8" ht="45" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>419</v>
-      </c>
-      <c r="B11">
-        <v>8.1304154901890406</v>
-      </c>
-      <c r="C11">
-        <v>0.13379913857126899</v>
+      <c r="A11" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B11" s="1">
+        <v>8.4368095561837997</v>
+      </c>
+      <c r="C11" s="1">
+        <v>0.14134057599559999</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>27</v>
@@ -9094,14 +9094,14 @@
       </c>
     </row>
     <row r="12" spans="1:8" ht="45" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>9</v>
-      </c>
-      <c r="B12">
-        <v>8.2121360213246692</v>
-      </c>
-      <c r="C12">
-        <v>0.135112188890431</v>
+      <c r="A12" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B12" s="1">
+        <v>8.4364141305933895</v>
+      </c>
+      <c r="C12" s="1">
+        <v>0.13854180631109</v>
       </c>
       <c r="F12" s="1" t="s">
         <v>418</v>
@@ -9114,14 +9114,14 @@
       </c>
     </row>
     <row r="13" spans="1:8" ht="45" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>420</v>
-      </c>
-      <c r="B13">
-        <v>8.2898703177931896</v>
-      </c>
-      <c r="C13">
-        <v>0.130316004197812</v>
+      <c r="A13" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B13" s="1">
+        <v>8.4084015562695207</v>
+      </c>
+      <c r="C13" s="1">
+        <v>0.13743837454275501</v>
       </c>
       <c r="F13" s="1" t="s">
         <v>419</v>
@@ -9134,14 +9134,14 @@
       </c>
     </row>
     <row r="14" spans="1:8" ht="45" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>10</v>
-      </c>
-      <c r="B14">
-        <v>8.3727208112640206</v>
-      </c>
-      <c r="C14">
-        <v>0.13498234565869699</v>
+      <c r="A14" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B14" s="1">
+        <v>8.5099572412062301</v>
+      </c>
+      <c r="C14" s="1">
+        <v>0.13738267695902801</v>
       </c>
       <c r="F14" s="1" t="s">
         <v>9</v>
@@ -9154,14 +9154,14 @@
       </c>
     </row>
     <row r="15" spans="1:8" ht="45" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>11</v>
-      </c>
-      <c r="B15">
-        <v>8.4364141305933895</v>
-      </c>
-      <c r="C15">
-        <v>0.13854180631109</v>
+      <c r="A15" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B15" s="1">
+        <v>8.4321434520724008</v>
+      </c>
+      <c r="C15" s="1">
+        <v>0.14159428045373601</v>
       </c>
       <c r="F15" s="1" t="s">
         <v>420</v>
@@ -9174,14 +9174,14 @@
       </c>
     </row>
     <row r="16" spans="1:8" ht="45" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>12</v>
-      </c>
-      <c r="B16">
-        <v>8.4084015562695207</v>
-      </c>
-      <c r="C16">
-        <v>0.13743837454275501</v>
+      <c r="A16" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B16" s="1">
+        <v>8.4721216638779193</v>
+      </c>
+      <c r="C16" s="1">
+        <v>0.14391242117178599</v>
       </c>
       <c r="F16" s="1" t="s">
         <v>10</v>
@@ -9193,29 +9193,29 @@
         <v>0.13498234565869699</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>13</v>
-      </c>
-      <c r="B17">
-        <v>8.5099572412062301</v>
-      </c>
-      <c r="C17">
-        <v>0.13738267695902801</v>
+    <row r="17" spans="1:8" ht="45" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B17" s="1">
+        <v>8.4953666075608503</v>
+      </c>
+      <c r="C17" s="1">
+        <v>0.13920272125085101</v>
       </c>
       <c r="G17" t="s">
         <v>385</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="45" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>14</v>
-      </c>
-      <c r="B18">
-        <v>8.4321434520724008</v>
-      </c>
-      <c r="C18">
-        <v>0.14159428045373601</v>
+      <c r="A18" s="1" t="s">
+        <v>421</v>
+      </c>
+      <c r="B18" s="1">
+        <v>8.5996727461700306</v>
+      </c>
+      <c r="C18" s="1">
+        <v>0.13915991329959099</v>
       </c>
       <c r="F18" s="1" t="s">
         <v>6</v>
@@ -9228,14 +9228,14 @@
       </c>
     </row>
     <row r="19" spans="1:8" ht="45" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>8</v>
-      </c>
-      <c r="B19">
-        <v>8.53551089338964</v>
-      </c>
-      <c r="C19">
-        <v>0.14232784705226301</v>
+      <c r="A19" s="1" t="s">
+        <v>422</v>
+      </c>
+      <c r="B19" s="1">
+        <v>8.6033820921791602</v>
+      </c>
+      <c r="C19" s="1">
+        <v>0.13928443937518301</v>
       </c>
       <c r="F19" s="1" t="s">
         <v>11</v>
@@ -9248,14 +9248,14 @@
       </c>
     </row>
     <row r="20" spans="1:8" ht="45" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>15</v>
-      </c>
-      <c r="B20">
-        <v>8.4721216638779193</v>
-      </c>
-      <c r="C20">
-        <v>0.14391242117178599</v>
+      <c r="A20" s="1" t="s">
+        <v>424</v>
+      </c>
+      <c r="B20" s="1">
+        <v>8.4545546426380405</v>
+      </c>
+      <c r="C20" s="1">
+        <v>0.14380448214622399</v>
       </c>
       <c r="F20" s="1" t="s">
         <v>12</v>
@@ -9268,14 +9268,14 @@
       </c>
     </row>
     <row r="21" spans="1:8" ht="45" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>16</v>
-      </c>
-      <c r="B21">
-        <v>8.4953666075608503</v>
-      </c>
-      <c r="C21">
-        <v>0.13920272125085101</v>
+      <c r="A21" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B21" s="1">
+        <v>8.5889106546587897</v>
+      </c>
+      <c r="C21" s="1">
+        <v>0.13910873933717599</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>13</v>
@@ -9288,14 +9288,14 @@
       </c>
     </row>
     <row r="22" spans="1:8" ht="45" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>17</v>
-      </c>
-      <c r="B22">
-        <v>8.7711252103094601</v>
-      </c>
-      <c r="C22">
-        <v>0.14459533841685501</v>
+      <c r="A22" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B22" s="1">
+        <v>8.5895120122534792</v>
+      </c>
+      <c r="C22" s="1">
+        <v>0.14198189433295499</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>14</v>
@@ -9308,14 +9308,14 @@
       </c>
     </row>
     <row r="23" spans="1:8" ht="45" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>421</v>
-      </c>
-      <c r="B23">
-        <v>8.5996727461700306</v>
-      </c>
-      <c r="C23">
-        <v>0.13915991329959099</v>
+      <c r="A23" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B23" s="1">
+        <v>8.6524212475503699</v>
+      </c>
+      <c r="C23" s="1">
+        <v>0.14200693706074399</v>
       </c>
       <c r="F23" s="1" t="s">
         <v>15</v>
@@ -9328,14 +9328,14 @@
       </c>
     </row>
     <row r="24" spans="1:8" ht="45" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>18</v>
-      </c>
-      <c r="B24">
-        <v>8.5801266895029205</v>
-      </c>
-      <c r="C24">
-        <v>0.144975058104169</v>
+      <c r="A24" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B24" s="1">
+        <v>8.6554109919161206</v>
+      </c>
+      <c r="C24" s="1">
+        <v>0.14287369952523299</v>
       </c>
       <c r="F24" s="1" t="s">
         <v>16</v>
@@ -9348,14 +9348,14 @@
       </c>
     </row>
     <row r="25" spans="1:8" ht="45" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>19</v>
-      </c>
-      <c r="B25">
-        <v>8.5783681642005494</v>
-      </c>
-      <c r="C25">
-        <v>0.14496624110967199</v>
+      <c r="A25" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B25" s="1">
+        <v>8.53551089338964</v>
+      </c>
+      <c r="C25" s="1">
+        <v>0.14232784705226301</v>
       </c>
       <c r="F25" s="1" t="s">
         <v>421</v>
@@ -9368,14 +9368,14 @@
       </c>
     </row>
     <row r="26" spans="1:8" ht="45" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>20</v>
-      </c>
-      <c r="B26">
-        <v>8.6129268121772302</v>
-      </c>
-      <c r="C26">
-        <v>0.14341121488491801</v>
+      <c r="A26" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B26" s="1">
+        <v>8.7711252103094601</v>
+      </c>
+      <c r="C26" s="1">
+        <v>0.14459533841685501</v>
       </c>
       <c r="F26" s="1" t="s">
         <v>422</v>
@@ -9388,14 +9388,14 @@
       </c>
     </row>
     <row r="27" spans="1:8" ht="45" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>21</v>
-      </c>
-      <c r="B27">
-        <v>8.6349505815443095</v>
-      </c>
-      <c r="C27">
-        <v>0.14388771373763901</v>
+      <c r="A27" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B27" s="1">
+        <v>8.5801266895029205</v>
+      </c>
+      <c r="C27" s="1">
+        <v>0.144975058104169</v>
       </c>
       <c r="F27" s="1" t="s">
         <v>424</v>
@@ -9408,14 +9408,14 @@
       </c>
     </row>
     <row r="28" spans="1:8" ht="45" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>22</v>
-      </c>
-      <c r="B28">
-        <v>8.5827352500219707</v>
-      </c>
-      <c r="C28">
-        <v>0.14091026017191899</v>
+      <c r="A28" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B28" s="1">
+        <v>8.5783681642005494</v>
+      </c>
+      <c r="C28" s="1">
+        <v>0.14496624110967199</v>
       </c>
       <c r="F28" s="1" t="s">
         <v>24</v>
@@ -9427,29 +9427,29 @@
         <v>0.13910873933717599</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>422</v>
-      </c>
-      <c r="B29">
-        <v>8.6033820921791602</v>
-      </c>
-      <c r="C29">
-        <v>0.13928443937518301</v>
+    <row r="29" spans="1:8" ht="45" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B29" s="1">
+        <v>8.6129268121772302</v>
+      </c>
+      <c r="C29" s="1">
+        <v>0.14341121488491801</v>
       </c>
       <c r="G29" t="s">
         <v>386</v>
       </c>
     </row>
     <row r="30" spans="1:8" ht="45" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>23</v>
-      </c>
-      <c r="B30">
-        <v>8.6784045244654298</v>
-      </c>
-      <c r="C30">
-        <v>0.14449758570660601</v>
+      <c r="A30" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B30" s="1">
+        <v>8.6349505815443095</v>
+      </c>
+      <c r="C30" s="1">
+        <v>0.14388771373763901</v>
       </c>
       <c r="F30" s="1" t="s">
         <v>3</v>
@@ -9462,14 +9462,14 @@
       </c>
     </row>
     <row r="31" spans="1:8" ht="45" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>423</v>
-      </c>
-      <c r="B31">
-        <v>8.6432150051153496</v>
-      </c>
-      <c r="C31">
-        <v>0.14272080636913501</v>
+      <c r="A31" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B31" s="1">
+        <v>8.5827352500219707</v>
+      </c>
+      <c r="C31" s="1">
+        <v>0.14091026017191899</v>
       </c>
       <c r="F31" s="1" t="s">
         <v>4</v>
@@ -9482,14 +9482,14 @@
       </c>
     </row>
     <row r="32" spans="1:8" ht="45" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>424</v>
-      </c>
-      <c r="B32">
-        <v>8.4545546426380405</v>
-      </c>
-      <c r="C32">
-        <v>0.14380448214622399</v>
+      <c r="A32" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B32" s="1">
+        <v>8.6784045244654298</v>
+      </c>
+      <c r="C32" s="1">
+        <v>0.14449758570660601</v>
       </c>
       <c r="F32" s="1" t="s">
         <v>7</v>
@@ -9502,14 +9502,14 @@
       </c>
     </row>
     <row r="33" spans="1:8" ht="45" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>24</v>
-      </c>
-      <c r="B33">
-        <v>8.5889106546587897</v>
-      </c>
-      <c r="C33">
-        <v>0.13910873933717599</v>
+      <c r="A33" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="B33" s="1">
+        <v>8.6432150051153496</v>
+      </c>
+      <c r="C33" s="1">
+        <v>0.14272080636913501</v>
       </c>
       <c r="F33" s="1" t="s">
         <v>8</v>
@@ -11540,939 +11540,927 @@
         <v>0.17654554655181801</v>
       </c>
     </row>
-    <row r="211" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B211" s="1"/>
-      <c r="C211" s="1"/>
-    </row>
-    <row r="212" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B212" s="1"/>
-      <c r="C212" s="1"/>
-    </row>
-    <row r="213" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B213" s="1"/>
-      <c r="C213" s="1"/>
+    <row r="211" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A211" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="B211" s="1">
+        <v>13.2697393001639</v>
+      </c>
+      <c r="C211" s="1">
+        <v>0.21689563024651701</v>
+      </c>
+    </row>
+    <row r="212" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A212" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="B212" s="1">
+        <v>13.085484930856</v>
+      </c>
+      <c r="C212" s="1">
+        <v>0.21250705902688999</v>
+      </c>
+    </row>
+    <row r="213" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A213" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="B213" s="1">
+        <v>13.175945695541801</v>
+      </c>
+      <c r="C213" s="1">
+        <v>0.21268324019514501</v>
+      </c>
     </row>
     <row r="214" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A214" s="1" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="B214" s="1">
-        <v>13.2697393001639</v>
+        <v>12.932688227182499</v>
       </c>
       <c r="C214" s="1">
-        <v>0.21689563024651701</v>
+        <v>0.21049345542616399</v>
       </c>
     </row>
     <row r="215" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A215" s="1" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="B215" s="1">
-        <v>13.085484930856</v>
+        <v>12.983441137506301</v>
       </c>
       <c r="C215" s="1">
-        <v>0.21250705902688999</v>
+        <v>0.214431740824571</v>
       </c>
     </row>
     <row r="216" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A216" s="1" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="B216" s="1">
-        <v>13.175945695541801</v>
+        <v>13.0765465639323</v>
       </c>
       <c r="C216" s="1">
-        <v>0.21268324019514501</v>
+        <v>0.21026943516751501</v>
       </c>
     </row>
     <row r="217" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A217" s="1" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="B217" s="1">
-        <v>12.932688227182499</v>
+        <v>13.1139776982864</v>
       </c>
       <c r="C217" s="1">
-        <v>0.21049345542616399</v>
+        <v>0.211983108185162</v>
       </c>
     </row>
     <row r="218" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A218" s="1" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="B218" s="1">
-        <v>12.983441137506301</v>
+        <v>13.148082507003</v>
       </c>
       <c r="C218" s="1">
-        <v>0.214431740824571</v>
+        <v>0.212540414406241</v>
       </c>
     </row>
     <row r="219" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A219" s="1" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="B219" s="1">
-        <v>13.0765465639323</v>
+        <v>12.9457941612001</v>
       </c>
       <c r="C219" s="1">
-        <v>0.21026943516751501</v>
+        <v>0.21316933311979799</v>
       </c>
     </row>
     <row r="220" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A220" s="1" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="B220" s="1">
-        <v>13.1139776982864</v>
+        <v>13.0137021255065</v>
       </c>
       <c r="C220" s="1">
-        <v>0.211983108185162</v>
+        <v>0.212515123863107</v>
       </c>
     </row>
     <row r="221" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A221" s="1" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="B221" s="1">
-        <v>13.148082507003</v>
+        <v>13.1418022843663</v>
       </c>
       <c r="C221" s="1">
-        <v>0.212540414406241</v>
+        <v>0.21030240285409901</v>
       </c>
     </row>
     <row r="222" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A222" s="1" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="B222" s="1">
-        <v>12.9457941612001</v>
+        <v>13.1707068509</v>
       </c>
       <c r="C222" s="1">
-        <v>0.21316933311979799</v>
+        <v>0.213000429148374</v>
       </c>
     </row>
     <row r="223" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A223" s="1" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="B223" s="1">
-        <v>13.0137021255065</v>
+        <v>13.2066468551924</v>
       </c>
       <c r="C223" s="1">
-        <v>0.212515123863107</v>
+        <v>0.21204120218539499</v>
       </c>
     </row>
     <row r="224" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A224" s="1" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="B224" s="1">
-        <v>13.1418022843663</v>
+        <v>13.158519557395699</v>
       </c>
       <c r="C224" s="1">
-        <v>0.21030240285409901</v>
+        <v>0.211005527878392</v>
       </c>
     </row>
     <row r="225" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A225" s="1" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="B225" s="1">
-        <v>13.1707068509</v>
+        <v>13.101689684028599</v>
       </c>
       <c r="C225" s="1">
-        <v>0.213000429148374</v>
+        <v>0.21490935202097999</v>
       </c>
     </row>
     <row r="226" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A226" s="1" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="B226" s="1">
-        <v>13.2066468551924</v>
+        <v>13.214174220163899</v>
       </c>
       <c r="C226" s="1">
-        <v>0.21204120218539499</v>
+        <v>0.214705500945685</v>
       </c>
     </row>
     <row r="227" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A227" s="1" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="B227" s="1">
-        <v>13.158519557395699</v>
+        <v>13.1096701956908</v>
       </c>
       <c r="C227" s="1">
-        <v>0.211005527878392</v>
+        <v>0.21046954774395399</v>
       </c>
     </row>
     <row r="228" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A228" s="1" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="B228" s="1">
-        <v>13.101689684028599</v>
+        <v>13.073395646730701</v>
       </c>
       <c r="C228" s="1">
-        <v>0.21490935202097999</v>
+        <v>0.212979730482002</v>
       </c>
     </row>
     <row r="229" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A229" s="1" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="B229" s="1">
-        <v>13.214174220163899</v>
+        <v>13.312833843466599</v>
       </c>
       <c r="C229" s="1">
-        <v>0.214705500945685</v>
+        <v>0.21145441547031901</v>
       </c>
     </row>
     <row r="230" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A230" s="1" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="B230" s="1">
-        <v>13.1096701956908</v>
+        <v>13.124987483828299</v>
       </c>
       <c r="C230" s="1">
-        <v>0.21046954774395399</v>
+        <v>0.21334229216903</v>
       </c>
     </row>
     <row r="231" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A231" s="1" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="B231" s="1">
-        <v>13.073395646730701</v>
+        <v>12.978247315348099</v>
       </c>
       <c r="C231" s="1">
-        <v>0.212979730482002</v>
+        <v>0.21313225436689001</v>
       </c>
     </row>
     <row r="232" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A232" s="1" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="B232" s="1">
-        <v>13.312833843466599</v>
+        <v>13.0256010563036</v>
       </c>
       <c r="C232" s="1">
-        <v>0.21145441547031901</v>
+        <v>0.21364986681269199</v>
       </c>
     </row>
     <row r="233" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A233" s="1" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="B233" s="1">
-        <v>13.124987483828299</v>
+        <v>12.962310430945999</v>
       </c>
       <c r="C233" s="1">
-        <v>0.21334229216903</v>
+        <v>0.21046298569896901</v>
       </c>
     </row>
     <row r="234" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A234" s="1" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="B234" s="1">
-        <v>12.978247315348099</v>
+        <v>13.003649574191501</v>
       </c>
       <c r="C234" s="1">
-        <v>0.21313225436689001</v>
+        <v>0.21370475343700501</v>
       </c>
     </row>
     <row r="235" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A235" s="1" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="B235" s="1">
-        <v>13.0256010563036</v>
+        <v>13.0669427926527</v>
       </c>
       <c r="C235" s="1">
-        <v>0.21364986681269199</v>
+        <v>0.213427613164866</v>
       </c>
     </row>
     <row r="236" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A236" s="1" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="B236" s="1">
-        <v>12.962310430945999</v>
+        <v>13.118146624426201</v>
       </c>
       <c r="C236" s="1">
-        <v>0.21046298569896901</v>
+        <v>0.21285885222227299</v>
       </c>
     </row>
     <row r="237" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A237" s="1" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="B237" s="1">
-        <v>13.003649574191501</v>
+        <v>13.061519052065201</v>
       </c>
       <c r="C237" s="1">
-        <v>0.21370475343700501</v>
+        <v>0.21229610722325801</v>
       </c>
     </row>
     <row r="238" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A238" s="1" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="B238" s="1">
-        <v>13.0669427926527</v>
+        <v>13.0135879028039</v>
       </c>
       <c r="C238" s="1">
-        <v>0.213427613164866</v>
+        <v>0.213479995323273</v>
       </c>
     </row>
     <row r="239" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A239" s="1" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="B239" s="1">
-        <v>13.118146624426201</v>
+        <v>14.610387851091801</v>
       </c>
       <c r="C239" s="1">
-        <v>0.21285885222227299</v>
+        <v>0.23747635372092801</v>
       </c>
     </row>
     <row r="240" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A240" s="1" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="B240" s="1">
-        <v>13.061519052065201</v>
+        <v>14.824645793302301</v>
       </c>
       <c r="C240" s="1">
-        <v>0.21229610722325801</v>
+        <v>0.24180291421483799</v>
       </c>
     </row>
     <row r="241" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A241" s="1" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="B241" s="1">
-        <v>13.0135879028039</v>
+        <v>14.4528707103913</v>
       </c>
       <c r="C241" s="1">
-        <v>0.213479995323273</v>
+        <v>0.23775144209915899</v>
       </c>
     </row>
     <row r="242" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A242" s="1" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="B242" s="1">
-        <v>14.610387851091801</v>
+        <v>14.6109532885724</v>
       </c>
       <c r="C242" s="1">
-        <v>0.23747635372092801</v>
+        <v>0.24065215342237201</v>
       </c>
     </row>
     <row r="243" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A243" s="1" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="B243" s="1">
-        <v>14.824645793302301</v>
+        <v>14.525535608882601</v>
       </c>
       <c r="C243" s="1">
-        <v>0.24180291421483799</v>
+        <v>0.238634580986853</v>
       </c>
     </row>
     <row r="244" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A244" s="1" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="B244" s="1">
-        <v>14.4528707103913</v>
+        <v>14.703570164436799</v>
       </c>
       <c r="C244" s="1">
-        <v>0.23775144209915899</v>
+        <v>0.24123516367901099</v>
       </c>
     </row>
     <row r="245" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A245" s="1" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="B245" s="1">
-        <v>14.6109532885724</v>
+        <v>14.6469605754983</v>
       </c>
       <c r="C245" s="1">
-        <v>0.24065215342237201</v>
+        <v>0.23838761262462899</v>
       </c>
     </row>
     <row r="246" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A246" s="1" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="B246" s="1">
-        <v>14.525535608882601</v>
+        <v>14.4430203101595</v>
       </c>
       <c r="C246" s="1">
-        <v>0.238634580986853</v>
+        <v>0.23787175668006799</v>
       </c>
     </row>
     <row r="247" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A247" s="1" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="B247" s="1">
-        <v>14.703570164436799</v>
+        <v>14.549598435905899</v>
       </c>
       <c r="C247" s="1">
-        <v>0.24123516367901099</v>
+        <v>0.235957408677299</v>
       </c>
     </row>
     <row r="248" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A248" s="1" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="B248" s="1">
-        <v>14.6469605754983</v>
+        <v>14.7043335718615</v>
       </c>
       <c r="C248" s="1">
-        <v>0.23838761262462899</v>
+        <v>0.23761103430247099</v>
       </c>
     </row>
     <row r="249" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A249" s="1" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="B249" s="1">
-        <v>14.4430203101595</v>
+        <v>14.770828981153199</v>
       </c>
       <c r="C249" s="1">
-        <v>0.23787175668006799</v>
+        <v>0.24049928819975</v>
       </c>
     </row>
     <row r="250" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A250" s="1" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="B250" s="1">
-        <v>14.549598435905899</v>
+        <v>14.7903674498711</v>
       </c>
       <c r="C250" s="1">
-        <v>0.235957408677299</v>
+        <v>0.23875237313230799</v>
       </c>
     </row>
     <row r="251" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A251" s="1" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="B251" s="1">
-        <v>14.7043335718615</v>
+        <v>14.6129136258226</v>
       </c>
       <c r="C251" s="1">
-        <v>0.23761103430247099</v>
+        <v>0.23577509684512599</v>
       </c>
     </row>
     <row r="252" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A252" s="1" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="B252" s="1">
-        <v>14.770828981153199</v>
+        <v>14.5285253520751</v>
       </c>
       <c r="C252" s="1">
-        <v>0.24049928819975</v>
+        <v>0.23798590162913699</v>
       </c>
     </row>
     <row r="253" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A253" s="1" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="B253" s="1">
-        <v>14.7903674498711</v>
+        <v>14.4495865267067</v>
       </c>
       <c r="C253" s="1">
-        <v>0.23875237313230799</v>
+        <v>0.23776270729380899</v>
       </c>
     </row>
     <row r="254" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A254" s="1" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="B254" s="1">
-        <v>14.6129136258226</v>
+        <v>14.524765784844201</v>
       </c>
       <c r="C254" s="1">
-        <v>0.23577509684512599</v>
+        <v>0.23525871098023601</v>
       </c>
     </row>
     <row r="255" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A255" s="1" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="B255" s="1">
-        <v>14.5285253520751</v>
+        <v>14.764112552014099</v>
       </c>
       <c r="C255" s="1">
-        <v>0.23798590162913699</v>
+        <v>0.23822698567085801</v>
       </c>
     </row>
     <row r="256" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A256" s="1" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="B256" s="1">
-        <v>14.4495865267067</v>
+        <v>14.7106184874969</v>
       </c>
       <c r="C256" s="1">
-        <v>0.23776270729380899</v>
+        <v>0.236137249858582</v>
       </c>
     </row>
     <row r="257" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A257" s="1" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="B257" s="1">
-        <v>14.524765784844201</v>
+        <v>14.749177714501</v>
       </c>
       <c r="C257" s="1">
-        <v>0.23525871098023601</v>
+        <v>0.236589149526167</v>
       </c>
     </row>
     <row r="258" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A258" s="1" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="B258" s="1">
-        <v>14.764112552014099</v>
+        <v>14.6684970880551</v>
       </c>
       <c r="C258" s="1">
-        <v>0.23822698567085801</v>
+        <v>0.234995035195148</v>
       </c>
     </row>
     <row r="259" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A259" s="1" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="B259" s="1">
-        <v>14.7106184874969</v>
+        <v>14.5764121579489</v>
       </c>
       <c r="C259" s="1">
-        <v>0.236137249858582</v>
+        <v>0.238435257488993</v>
       </c>
     </row>
     <row r="260" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A260" s="1" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="B260" s="1">
-        <v>14.749177714501</v>
+        <v>14.633716179029699</v>
       </c>
       <c r="C260" s="1">
-        <v>0.236589149526167</v>
+        <v>0.23631298859917599</v>
       </c>
     </row>
     <row r="261" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A261" s="1" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="B261" s="1">
-        <v>14.6684970880551</v>
+        <v>14.618198212113001</v>
       </c>
       <c r="C261" s="1">
-        <v>0.234995035195148</v>
+        <v>0.238968925765909</v>
       </c>
     </row>
     <row r="262" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A262" s="1" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="B262" s="1">
-        <v>14.5764121579489</v>
+        <v>14.482642723981799</v>
       </c>
       <c r="C262" s="1">
-        <v>0.238435257488993</v>
+        <v>0.237506075673066</v>
       </c>
     </row>
     <row r="263" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A263" s="1" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="B263" s="1">
-        <v>14.633716179029699</v>
+        <v>14.491750683935599</v>
       </c>
       <c r="C263" s="1">
-        <v>0.23631298859917599</v>
+        <v>0.237718713583811</v>
       </c>
     </row>
     <row r="264" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A264" s="1" t="s">
-        <v>255</v>
+        <v>387</v>
       </c>
       <c r="B264" s="1">
-        <v>14.618198212113001</v>
+        <v>17.825013007136501</v>
       </c>
       <c r="C264" s="1">
-        <v>0.238968925765909</v>
+        <v>0.29193451692567801</v>
       </c>
     </row>
     <row r="265" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A265" s="1" t="s">
-        <v>256</v>
+        <v>388</v>
       </c>
       <c r="B265" s="1">
-        <v>14.482642723981799</v>
+        <v>17.9319730766783</v>
       </c>
       <c r="C265" s="1">
-        <v>0.237506075673066</v>
+        <v>0.28873287738484599</v>
       </c>
     </row>
     <row r="266" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A266" s="1" t="s">
-        <v>257</v>
+        <v>389</v>
       </c>
       <c r="B266" s="1">
-        <v>14.491750683935599</v>
+        <v>18.039044650769</v>
       </c>
       <c r="C266" s="1">
-        <v>0.237718713583811</v>
+        <v>0.28985427653153101</v>
       </c>
     </row>
     <row r="267" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A267" s="1" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="B267" s="1">
-        <v>17.825013007136501</v>
+        <v>18.0604756933053</v>
       </c>
       <c r="C267" s="1">
-        <v>0.29193451692567801</v>
+        <v>0.29473582812057803</v>
       </c>
     </row>
     <row r="268" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A268" s="1" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="B268" s="1">
-        <v>17.9319730766783</v>
+        <v>17.9979172106978</v>
       </c>
       <c r="C268" s="1">
-        <v>0.28873287738484599</v>
+        <v>0.29630016894823502</v>
       </c>
     </row>
     <row r="269" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A269" s="1" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="B269" s="1">
-        <v>18.039044650769</v>
+        <v>17.998827423434999</v>
       </c>
       <c r="C269" s="1">
-        <v>0.28985427653153101</v>
+        <v>0.290375757335809</v>
       </c>
     </row>
     <row r="270" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A270" s="1" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="B270" s="1">
-        <v>18.0604756933053</v>
+        <v>18.041509768701101</v>
       </c>
       <c r="C270" s="1">
-        <v>0.29473582812057803</v>
+        <v>0.29184259037329402</v>
       </c>
     </row>
     <row r="271" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A271" s="1" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="B271" s="1">
-        <v>17.9979172106978</v>
+        <v>18.113057907959</v>
       </c>
       <c r="C271" s="1">
-        <v>0.29630016894823502</v>
+        <v>0.29495272762742802</v>
       </c>
     </row>
     <row r="272" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A272" s="1" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="B272" s="1">
-        <v>17.998827423434999</v>
+        <v>18.000340035364701</v>
       </c>
       <c r="C272" s="1">
-        <v>0.290375757335809</v>
+        <v>0.29546767207366198</v>
       </c>
     </row>
     <row r="273" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A273" s="1" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="B273" s="1">
-        <v>18.041509768701101</v>
+        <v>18.056008326627001</v>
       </c>
       <c r="C273" s="1">
-        <v>0.29184259037329402</v>
+        <v>0.29613521382059799</v>
       </c>
     </row>
     <row r="274" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A274" s="1" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="B274" s="1">
-        <v>18.113057907959</v>
+        <v>18.143480906181601</v>
       </c>
       <c r="C274" s="1">
-        <v>0.29495272762742802</v>
+        <v>0.29582825670155199</v>
       </c>
     </row>
     <row r="275" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A275" s="1" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="B275" s="1">
-        <v>18.000340035364701</v>
+        <v>18.0505063076521</v>
       </c>
       <c r="C275" s="1">
-        <v>0.29546767207366198</v>
+        <v>0.29449530569974303</v>
       </c>
     </row>
     <row r="276" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A276" s="1" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="B276" s="1">
-        <v>18.056008326627001</v>
+        <v>17.975837914720699</v>
       </c>
       <c r="C276" s="1">
-        <v>0.29613521382059799</v>
+        <v>0.29806425275037302</v>
       </c>
     </row>
     <row r="277" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A277" s="1" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="B277" s="1">
-        <v>18.143480906181601</v>
+        <v>17.958408612980101</v>
       </c>
       <c r="C277" s="1">
-        <v>0.29582825670155199</v>
+        <v>0.29361605170472399</v>
       </c>
     </row>
     <row r="278" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A278" s="1" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="B278" s="1">
-        <v>18.0505063076521</v>
+        <v>18.089794941394199</v>
       </c>
       <c r="C278" s="1">
-        <v>0.29449530569974303</v>
+        <v>0.29750345759486801</v>
       </c>
     </row>
     <row r="279" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A279" s="1" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="B279" s="1">
-        <v>17.975837914720699</v>
+        <v>18.011107051113001</v>
       </c>
       <c r="C279" s="1">
-        <v>0.29806425275037302</v>
+        <v>0.29221770492358401</v>
       </c>
     </row>
     <row r="280" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A280" s="1" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="B280" s="1">
-        <v>17.958408612980101</v>
+        <v>18.059805482066999</v>
       </c>
       <c r="C280" s="1">
-        <v>0.29361605170472399</v>
+        <v>0.29462962623990302</v>
       </c>
     </row>
     <row r="281" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A281" s="1" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="B281" s="1">
-        <v>18.089794941394199</v>
+        <v>17.9483749982906</v>
       </c>
       <c r="C281" s="1">
-        <v>0.29750345759486801</v>
+        <v>0.29592312403825599</v>
       </c>
     </row>
     <row r="282" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A282" s="1" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="B282" s="1">
-        <v>18.011107051113001</v>
+        <v>17.986594818813899</v>
       </c>
       <c r="C282" s="1">
-        <v>0.29221770492358401</v>
+        <v>0.29448024773360298</v>
       </c>
     </row>
     <row r="283" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A283" s="1" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="B283" s="1">
-        <v>18.059805482066999</v>
+        <v>18.0136321630971</v>
       </c>
       <c r="C283" s="1">
-        <v>0.29462962623990302</v>
+        <v>0.29587930445673999</v>
       </c>
     </row>
     <row r="284" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A284" s="1" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="B284" s="1">
-        <v>17.9483749982906</v>
+        <v>18.175378572568899</v>
       </c>
       <c r="C284" s="1">
-        <v>0.29592312403825599</v>
+        <v>0.28842517989208999</v>
       </c>
     </row>
     <row r="285" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A285" s="1" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="B285" s="1">
-        <v>17.986594818813899</v>
+        <v>18.118575471661899</v>
       </c>
       <c r="C285" s="1">
-        <v>0.29448024773360298</v>
+        <v>0.29360342062414901</v>
       </c>
     </row>
     <row r="286" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A286" s="1" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="B286" s="1">
-        <v>18.0136321630971</v>
+        <v>17.929983986435602</v>
       </c>
       <c r="C286" s="1">
-        <v>0.29587930445673999</v>
+        <v>0.28921987206488498</v>
       </c>
     </row>
     <row r="287" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A287" s="1" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="B287" s="1">
-        <v>18.175378572568899</v>
+        <v>18.106604307150199</v>
       </c>
       <c r="C287" s="1">
-        <v>0.28842517989208999</v>
+        <v>0.29134851176696303</v>
       </c>
     </row>
     <row r="288" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A288" s="1" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="B288" s="1">
-        <v>18.118575471661899</v>
+        <v>17.996855885347902</v>
       </c>
       <c r="C288" s="1">
-        <v>0.29360342062414901</v>
+        <v>0.29264779346075898</v>
       </c>
     </row>
     <row r="289" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A289" s="1" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="B289" s="1">
-        <v>17.929983986435602</v>
+        <v>18.121396667491499</v>
       </c>
       <c r="C289" s="1">
-        <v>0.28921987206488498</v>
+        <v>0.28825504808202801</v>
       </c>
     </row>
     <row r="290" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A290" s="1" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="B290" s="1">
-        <v>18.106604307150199</v>
+        <v>18.094216738234799</v>
       </c>
       <c r="C290" s="1">
-        <v>0.29134851176696303</v>
+        <v>0.29422715038680303</v>
       </c>
     </row>
     <row r="291" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A291" s="1" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="B291" s="1">
-        <v>17.996855885347902</v>
+        <v>18.1174045096291</v>
       </c>
       <c r="C291" s="1">
-        <v>0.29264779346075898</v>
+        <v>0.295993095562951</v>
       </c>
     </row>
     <row r="292" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A292" s="1" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="B292" s="1">
-        <v>18.121396667491499</v>
+        <v>17.975345051957699</v>
       </c>
       <c r="C292" s="1">
-        <v>0.28825504808202801</v>
+        <v>0.291643296428021</v>
       </c>
     </row>
     <row r="293" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A293" s="1" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="B293" s="1">
-        <v>18.094216738234799</v>
+        <v>18.0641154539816</v>
       </c>
       <c r="C293" s="1">
-        <v>0.29422715038680303</v>
+        <v>0.29408431924388001</v>
       </c>
     </row>
     <row r="294" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A294" s="1" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="B294" s="1">
-        <v>18.1174045096291</v>
+        <v>18.268545430641002</v>
       </c>
       <c r="C294" s="1">
-        <v>0.295993095562951</v>
-      </c>
-    </row>
-    <row r="295" spans="1:3" ht="45" x14ac:dyDescent="0.25">
-      <c r="A295" s="1" t="s">
-        <v>415</v>
-      </c>
-      <c r="B295" s="1">
-        <v>17.975345051957699</v>
-      </c>
-      <c r="C295" s="1">
-        <v>0.291643296428021</v>
-      </c>
-    </row>
-    <row r="296" spans="1:3" ht="45" x14ac:dyDescent="0.25">
-      <c r="A296" s="1" t="s">
-        <v>416</v>
-      </c>
-      <c r="B296" s="1">
-        <v>18.0641154539816</v>
-      </c>
-      <c r="C296" s="1">
-        <v>0.29408431924388001</v>
-      </c>
-    </row>
-    <row r="297" spans="1:3" ht="45" x14ac:dyDescent="0.25">
-      <c r="A297" s="1" t="s">
-        <v>417</v>
-      </c>
-      <c r="B297" s="1">
-        <v>18.268545430641002</v>
-      </c>
-      <c r="C297" s="1">
         <v>0.29215304331091801</v>
       </c>
     </row>

--- a/Fit Results/Together.xlsx
+++ b/Fit Results/Together.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Diego\git\6s7p\Fit Results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF4CA369-446C-4A68-9325-CA745075709C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CB3AFA2-F014-4F57-99B2-C1723C059247}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="F1=3" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="460" uniqueCount="425">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="528" uniqueCount="493">
   <si>
     <t>Date</t>
   </si>
@@ -1315,6 +1315,210 @@
   </si>
   <si>
     <t>Jun09,2026+4-42-24PM</t>
+  </si>
+  <si>
+    <t>Jul08,2026+12-04-19PM</t>
+  </si>
+  <si>
+    <t>Jul08,2026+12-13-04PM</t>
+  </si>
+  <si>
+    <t>Jul08,2026+12-23-13PM</t>
+  </si>
+  <si>
+    <t>Jul08,2026+12-33-05PM</t>
+  </si>
+  <si>
+    <t>Jul08,2026+12-45-35PM</t>
+  </si>
+  <si>
+    <t>Jul08,2026+1-28-32PM</t>
+  </si>
+  <si>
+    <t>Jul08,2026+1-38-22PM</t>
+  </si>
+  <si>
+    <t>Jul08,2026+1-48-06PM</t>
+  </si>
+  <si>
+    <t>Jul08,2026+1-56-02PM</t>
+  </si>
+  <si>
+    <t>Jul08,2026+2-06-11PM</t>
+  </si>
+  <si>
+    <t>Jul08,2026+2-15-37PM</t>
+  </si>
+  <si>
+    <t>Jul08,2026+2-24-59PM</t>
+  </si>
+  <si>
+    <t>Jul08,2026+2-35-16PM</t>
+  </si>
+  <si>
+    <t>Jul08,2026+2-43-10PM</t>
+  </si>
+  <si>
+    <t>Jul08,2026+2-55-30PM</t>
+  </si>
+  <si>
+    <t>Jul08,2026+3-03-23PM</t>
+  </si>
+  <si>
+    <t>Jul08,2026+3-11-24PM</t>
+  </si>
+  <si>
+    <t>Jul08,2026+3-19-30PM</t>
+  </si>
+  <si>
+    <t>Jul08,2026+3-27-25PM</t>
+  </si>
+  <si>
+    <t>Jul08,2026+3-36-17PM</t>
+  </si>
+  <si>
+    <t>Jul08,2026+3-44-12PM</t>
+  </si>
+  <si>
+    <t>Jul08,2026+3-52-06PM</t>
+  </si>
+  <si>
+    <t>Jul08,2026+4-00-09PM</t>
+  </si>
+  <si>
+    <t>Jul08,2026+4-08-00PM</t>
+  </si>
+  <si>
+    <t>Jul08,2026+4-16-03PM</t>
+  </si>
+  <si>
+    <t>Jul08,2026+4-25-55PM</t>
+  </si>
+  <si>
+    <t>Jul08,2026+4-34-13PM</t>
+  </si>
+  <si>
+    <t>Jul08,2026+4-42-30PM</t>
+  </si>
+  <si>
+    <t>Jul08,2026+4-55-05PM</t>
+  </si>
+  <si>
+    <t>Jul08,2026+5-02-57PM</t>
+  </si>
+  <si>
+    <t>Jul08,2026+5-10-49PM</t>
+  </si>
+  <si>
+    <t>Jul08,2026+5-18-47PM</t>
+  </si>
+  <si>
+    <t>Jul09,2026+10-26-36AM</t>
+  </si>
+  <si>
+    <t>Jul09,2026+10-36-23AM</t>
+  </si>
+  <si>
+    <t>Jul09,2026+10-47-02AM</t>
+  </si>
+  <si>
+    <t>Jul09,2026+11-01-15AM</t>
+  </si>
+  <si>
+    <t>Jul09,2026+11-09-20AM</t>
+  </si>
+  <si>
+    <t>Jul09,2026+11-17-22AM</t>
+  </si>
+  <si>
+    <t>Jul09,2026+11-25-55AM</t>
+  </si>
+  <si>
+    <t>Jul09,2026+11-43-59AM</t>
+  </si>
+  <si>
+    <t>Jul09,2026+11-51-58AM</t>
+  </si>
+  <si>
+    <t>Jul09,2026+12-08-01PM</t>
+  </si>
+  <si>
+    <t>Jul09,2026+12-16-09PM</t>
+  </si>
+  <si>
+    <t>Jul09,2026+12-24-11PM</t>
+  </si>
+  <si>
+    <t>Jul09,2026+12-36-13PM</t>
+  </si>
+  <si>
+    <t>Jul09,2026+12-44-32PM</t>
+  </si>
+  <si>
+    <t>Jul09,2026+12-52-26PM</t>
+  </si>
+  <si>
+    <t>Jul09,2026+1-01-10PM</t>
+  </si>
+  <si>
+    <t>Jul09,2026+1-09-54PM</t>
+  </si>
+  <si>
+    <t>Jul09,2026+1-18-10PM</t>
+  </si>
+  <si>
+    <t>Jul09,2026+1-32-09PM</t>
+  </si>
+  <si>
+    <t>Jul09,2026+1-44-19PM</t>
+  </si>
+  <si>
+    <t>Jul09,2026+1-55-45PM</t>
+  </si>
+  <si>
+    <t>Jul09,2026+2-03-45PM</t>
+  </si>
+  <si>
+    <t>Jul09,2026+2-11-46PM</t>
+  </si>
+  <si>
+    <t>Jul09,2026+2-22-27PM</t>
+  </si>
+  <si>
+    <t>Jul09,2026+2-30-42PM</t>
+  </si>
+  <si>
+    <t>Jul09,2026+2-40-05PM</t>
+  </si>
+  <si>
+    <t>Jul09,2026+2-48-12PM</t>
+  </si>
+  <si>
+    <t>Jul09,2026+2-56-12PM</t>
+  </si>
+  <si>
+    <t>Jul09,2026+3-04-17PM</t>
+  </si>
+  <si>
+    <t>Jul09,2026+3-15-03PM</t>
+  </si>
+  <si>
+    <t>Jul09,2026+3-25-49PM</t>
+  </si>
+  <si>
+    <t>Jul09,2026+3-38-53PM</t>
+  </si>
+  <si>
+    <t>Jul09,2026+3-46-49PM</t>
+  </si>
+  <si>
+    <t>Jul09,2026+3-54-43PM</t>
+  </si>
+  <si>
+    <t>Jul09,2026+4-02-42PM</t>
+  </si>
+  <si>
+    <t>Jul09,2026+4-10-46PM</t>
   </si>
 </sst>
 </file>
@@ -12472,7 +12676,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{50FB9BA1-1961-4714-B0B7-8B6F37F6875A}">
-  <dimension ref="A1:C125"/>
+  <dimension ref="A1:C193"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:3" ht="30" x14ac:dyDescent="0.25">
@@ -13848,6 +14052,754 @@
       </c>
       <c r="C125" s="1">
         <v>0.24367652321245201</v>
+      </c>
+    </row>
+    <row r="126" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A126" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="B126" s="1">
+        <v>2.07892749786477</v>
+      </c>
+      <c r="C126" s="1">
+        <v>3.30028948262861E-2</v>
+      </c>
+    </row>
+    <row r="127" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A127" s="1" t="s">
+        <v>426</v>
+      </c>
+      <c r="B127" s="1">
+        <v>2.0663834161140699</v>
+      </c>
+      <c r="C127" s="1">
+        <v>3.3489889357849002E-2</v>
+      </c>
+    </row>
+    <row r="128" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A128" s="1" t="s">
+        <v>427</v>
+      </c>
+      <c r="B128" s="1">
+        <v>2.0628293519735901</v>
+      </c>
+      <c r="C128" s="1">
+        <v>3.34050697248311E-2</v>
+      </c>
+    </row>
+    <row r="129" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A129" s="1" t="s">
+        <v>428</v>
+      </c>
+      <c r="B129" s="1">
+        <v>2.07368391485078</v>
+      </c>
+      <c r="C129" s="1">
+        <v>3.3663016244114899E-2</v>
+      </c>
+    </row>
+    <row r="130" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A130" s="1" t="s">
+        <v>429</v>
+      </c>
+      <c r="B130" s="1">
+        <v>2.1039341660075501</v>
+      </c>
+      <c r="C130" s="1">
+        <v>3.3862208744561598E-2</v>
+      </c>
+    </row>
+    <row r="131" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A131" s="1" t="s">
+        <v>430</v>
+      </c>
+      <c r="B131" s="1">
+        <v>2.0673577404721302</v>
+      </c>
+      <c r="C131" s="1">
+        <v>3.3371230140689601E-2</v>
+      </c>
+    </row>
+    <row r="132" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A132" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="B132" s="1">
+        <v>2.0619952490668201</v>
+      </c>
+      <c r="C132" s="1">
+        <v>3.3958687307630298E-2</v>
+      </c>
+    </row>
+    <row r="133" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A133" s="1" t="s">
+        <v>432</v>
+      </c>
+      <c r="B133" s="1">
+        <v>2.05981399507903</v>
+      </c>
+      <c r="C133" s="1">
+        <v>3.3717539743101703E-2</v>
+      </c>
+    </row>
+    <row r="134" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A134" s="1" t="s">
+        <v>433</v>
+      </c>
+      <c r="B134" s="1">
+        <v>2.0609859200885801</v>
+      </c>
+      <c r="C134" s="1">
+        <v>3.4019624541611997E-2</v>
+      </c>
+    </row>
+    <row r="135" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A135" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="B135" s="1">
+        <v>2.0594671215384501</v>
+      </c>
+      <c r="C135" s="1">
+        <v>3.30325465399912E-2</v>
+      </c>
+    </row>
+    <row r="136" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A136" s="1" t="s">
+        <v>435</v>
+      </c>
+      <c r="B136" s="1">
+        <v>2.07614752547159</v>
+      </c>
+      <c r="C136" s="1">
+        <v>3.3342495220022902E-2</v>
+      </c>
+    </row>
+    <row r="137" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A137" s="1" t="s">
+        <v>436</v>
+      </c>
+      <c r="B137" s="1">
+        <v>2.0785120893459799</v>
+      </c>
+      <c r="C137" s="1">
+        <v>3.3765726933882197E-2</v>
+      </c>
+    </row>
+    <row r="138" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A138" s="1" t="s">
+        <v>437</v>
+      </c>
+      <c r="B138" s="1">
+        <v>2.0891336228459898</v>
+      </c>
+      <c r="C138" s="1">
+        <v>3.3827431022495302E-2</v>
+      </c>
+    </row>
+    <row r="139" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A139" s="1" t="s">
+        <v>438</v>
+      </c>
+      <c r="B139" s="1">
+        <v>2.0903682617926802</v>
+      </c>
+      <c r="C139" s="1">
+        <v>3.2562436603975398E-2</v>
+      </c>
+    </row>
+    <row r="140" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A140" s="1" t="s">
+        <v>439</v>
+      </c>
+      <c r="B140" s="1">
+        <v>2.10180294618258</v>
+      </c>
+      <c r="C140" s="1">
+        <v>3.3936476228758998E-2</v>
+      </c>
+    </row>
+    <row r="141" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A141" s="1" t="s">
+        <v>440</v>
+      </c>
+      <c r="B141" s="1">
+        <v>2.1021592068839001</v>
+      </c>
+      <c r="C141" s="1">
+        <v>3.3445511192293297E-2</v>
+      </c>
+    </row>
+    <row r="142" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A142" s="1" t="s">
+        <v>441</v>
+      </c>
+      <c r="B142" s="1">
+        <v>2.1003895957887599</v>
+      </c>
+      <c r="C142" s="1">
+        <v>3.3061817051389601E-2</v>
+      </c>
+    </row>
+    <row r="143" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A143" s="1" t="s">
+        <v>442</v>
+      </c>
+      <c r="B143" s="1">
+        <v>2.0968436651486999</v>
+      </c>
+      <c r="C143" s="1">
+        <v>3.35542069970673E-2</v>
+      </c>
+    </row>
+    <row r="144" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A144" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="B144" s="1">
+        <v>2.0879161684316299</v>
+      </c>
+      <c r="C144" s="1">
+        <v>3.4176849718869903E-2</v>
+      </c>
+    </row>
+    <row r="145" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A145" s="1" t="s">
+        <v>444</v>
+      </c>
+      <c r="B145" s="1">
+        <v>2.0889443536633001</v>
+      </c>
+      <c r="C145" s="1">
+        <v>3.3607525034085699E-2</v>
+      </c>
+    </row>
+    <row r="146" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A146" s="1" t="s">
+        <v>445</v>
+      </c>
+      <c r="B146" s="1">
+        <v>2.0788690207312501</v>
+      </c>
+      <c r="C146" s="1">
+        <v>3.3291217503168297E-2</v>
+      </c>
+    </row>
+    <row r="147" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A147" s="1" t="s">
+        <v>446</v>
+      </c>
+      <c r="B147" s="1">
+        <v>2.0777810140456099</v>
+      </c>
+      <c r="C147" s="1">
+        <v>3.3587626783338299E-2</v>
+      </c>
+    </row>
+    <row r="148" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A148" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="B148" s="1">
+        <v>2.0773479287857999</v>
+      </c>
+      <c r="C148" s="1">
+        <v>3.3498059501305001E-2</v>
+      </c>
+    </row>
+    <row r="149" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A149" s="1" t="s">
+        <v>448</v>
+      </c>
+      <c r="B149" s="1">
+        <v>2.0750460102786898</v>
+      </c>
+      <c r="C149" s="1">
+        <v>3.3612378265113999E-2</v>
+      </c>
+    </row>
+    <row r="150" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A150" s="1" t="s">
+        <v>449</v>
+      </c>
+      <c r="B150" s="1">
+        <v>2.07579422159953</v>
+      </c>
+      <c r="C150" s="1">
+        <v>3.36767838831264E-2</v>
+      </c>
+    </row>
+    <row r="151" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A151" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="B151" s="1">
+        <v>2.0691590991764399</v>
+      </c>
+      <c r="C151" s="1">
+        <v>3.4205246508627503E-2</v>
+      </c>
+    </row>
+    <row r="152" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A152" s="1" t="s">
+        <v>451</v>
+      </c>
+      <c r="B152" s="1">
+        <v>2.0830929433282899</v>
+      </c>
+      <c r="C152" s="1">
+        <v>3.33159042246957E-2</v>
+      </c>
+    </row>
+    <row r="153" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A153" s="1" t="s">
+        <v>452</v>
+      </c>
+      <c r="B153" s="1">
+        <v>2.0711249818440698</v>
+      </c>
+      <c r="C153" s="1">
+        <v>3.4310317322257401E-2</v>
+      </c>
+    </row>
+    <row r="154" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A154" s="1" t="s">
+        <v>453</v>
+      </c>
+      <c r="B154" s="1">
+        <v>2.0663816479454802</v>
+      </c>
+      <c r="C154" s="1">
+        <v>3.4082317162395397E-2</v>
+      </c>
+    </row>
+    <row r="155" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A155" s="1" t="s">
+        <v>454</v>
+      </c>
+      <c r="B155" s="1">
+        <v>2.0640815890017499</v>
+      </c>
+      <c r="C155" s="1">
+        <v>3.3309537312556703E-2</v>
+      </c>
+    </row>
+    <row r="156" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A156" s="1" t="s">
+        <v>455</v>
+      </c>
+      <c r="B156" s="1">
+        <v>2.0662267195881898</v>
+      </c>
+      <c r="C156" s="1">
+        <v>3.2808961198641698E-2</v>
+      </c>
+    </row>
+    <row r="157" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A157" s="1" t="s">
+        <v>456</v>
+      </c>
+      <c r="B157" s="1">
+        <v>2.0714341542752299</v>
+      </c>
+      <c r="C157" s="1">
+        <v>3.3324024754485697E-2</v>
+      </c>
+    </row>
+    <row r="158" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A158" s="1" t="s">
+        <v>457</v>
+      </c>
+      <c r="B158" s="1">
+        <v>2.5011187965916499</v>
+      </c>
+      <c r="C158" s="1">
+        <v>4.0620494830716898E-2</v>
+      </c>
+    </row>
+    <row r="159" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A159" s="1" t="s">
+        <v>458</v>
+      </c>
+      <c r="B159" s="1">
+        <v>2.5056585895299199</v>
+      </c>
+      <c r="C159" s="1">
+        <v>4.0445250720025597E-2</v>
+      </c>
+    </row>
+    <row r="160" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A160" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="B160" s="1">
+        <v>2.48638142466051</v>
+      </c>
+      <c r="C160" s="1">
+        <v>4.0191516108636097E-2</v>
+      </c>
+    </row>
+    <row r="161" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A161" s="1" t="s">
+        <v>460</v>
+      </c>
+      <c r="B161" s="1">
+        <v>2.4855190794760902</v>
+      </c>
+      <c r="C161" s="1">
+        <v>4.0970033814296203E-2</v>
+      </c>
+    </row>
+    <row r="162" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A162" s="1" t="s">
+        <v>461</v>
+      </c>
+      <c r="B162" s="1">
+        <v>2.5074216201399602</v>
+      </c>
+      <c r="C162" s="1">
+        <v>4.04373053253217E-2</v>
+      </c>
+    </row>
+    <row r="163" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A163" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="B163" s="1">
+        <v>2.4877440696740298</v>
+      </c>
+      <c r="C163" s="1">
+        <v>4.0649065132095999E-2</v>
+      </c>
+    </row>
+    <row r="164" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A164" s="1" t="s">
+        <v>463</v>
+      </c>
+      <c r="B164" s="1">
+        <v>2.4798485643611698</v>
+      </c>
+      <c r="C164" s="1">
+        <v>3.9533611139950402E-2</v>
+      </c>
+    </row>
+    <row r="165" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A165" s="1" t="s">
+        <v>464</v>
+      </c>
+      <c r="B165" s="1">
+        <v>2.5040935191620002</v>
+      </c>
+      <c r="C165" s="1">
+        <v>4.0155853483306803E-2</v>
+      </c>
+    </row>
+    <row r="166" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A166" s="1" t="s">
+        <v>465</v>
+      </c>
+      <c r="B166" s="1">
+        <v>2.5154540630727702</v>
+      </c>
+      <c r="C166" s="1">
+        <v>4.0445594269577098E-2</v>
+      </c>
+    </row>
+    <row r="167" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A167" s="1" t="s">
+        <v>466</v>
+      </c>
+      <c r="B167" s="1">
+        <v>2.5215314979177399</v>
+      </c>
+      <c r="C167" s="1">
+        <v>3.9604033537862203E-2</v>
+      </c>
+    </row>
+    <row r="168" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A168" s="1" t="s">
+        <v>467</v>
+      </c>
+      <c r="B168" s="1">
+        <v>2.5255084560658201</v>
+      </c>
+      <c r="C168" s="1">
+        <v>4.0174033834531497E-2</v>
+      </c>
+    </row>
+    <row r="169" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A169" s="1" t="s">
+        <v>468</v>
+      </c>
+      <c r="B169" s="1">
+        <v>2.5217723144817001</v>
+      </c>
+      <c r="C169" s="1">
+        <v>4.1231746357817303E-2</v>
+      </c>
+    </row>
+    <row r="170" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A170" s="1" t="s">
+        <v>469</v>
+      </c>
+      <c r="B170" s="1">
+        <v>2.5063570266102602</v>
+      </c>
+      <c r="C170" s="1">
+        <v>4.0336571538600499E-2</v>
+      </c>
+    </row>
+    <row r="171" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A171" s="1" t="s">
+        <v>470</v>
+      </c>
+      <c r="B171" s="1">
+        <v>2.5171411510981598</v>
+      </c>
+      <c r="C171" s="1">
+        <v>4.0359240284840503E-2</v>
+      </c>
+    </row>
+    <row r="172" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A172" s="1" t="s">
+        <v>471</v>
+      </c>
+      <c r="B172" s="1">
+        <v>2.5186758172382802</v>
+      </c>
+      <c r="C172" s="1">
+        <v>4.0249713225980401E-2</v>
+      </c>
+    </row>
+    <row r="173" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A173" s="1" t="s">
+        <v>472</v>
+      </c>
+      <c r="B173" s="1">
+        <v>2.54554864229272</v>
+      </c>
+      <c r="C173" s="1">
+        <v>4.0520690948023297E-2</v>
+      </c>
+    </row>
+    <row r="174" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A174" s="1" t="s">
+        <v>473</v>
+      </c>
+      <c r="B174" s="1">
+        <v>2.54463980757486</v>
+      </c>
+      <c r="C174" s="1">
+        <v>4.02329856985481E-2</v>
+      </c>
+    </row>
+    <row r="175" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A175" s="1" t="s">
+        <v>474</v>
+      </c>
+      <c r="B175" s="1">
+        <v>2.5166341388295401</v>
+      </c>
+      <c r="C175" s="1">
+        <v>4.0144847093634903E-2</v>
+      </c>
+    </row>
+    <row r="176" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A176" s="1" t="s">
+        <v>475</v>
+      </c>
+      <c r="B176" s="1">
+        <v>2.52355147173308</v>
+      </c>
+      <c r="C176" s="1">
+        <v>4.0409209035940002E-2</v>
+      </c>
+    </row>
+    <row r="177" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A177" s="1" t="s">
+        <v>476</v>
+      </c>
+      <c r="B177" s="1">
+        <v>2.5237166224547098</v>
+      </c>
+      <c r="C177" s="1">
+        <v>4.10395989464786E-2</v>
+      </c>
+    </row>
+    <row r="178" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A178" s="1" t="s">
+        <v>477</v>
+      </c>
+      <c r="B178" s="1">
+        <v>2.5134774644318001</v>
+      </c>
+      <c r="C178" s="1">
+        <v>3.98714030158333E-2</v>
+      </c>
+    </row>
+    <row r="179" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A179" s="1" t="s">
+        <v>478</v>
+      </c>
+      <c r="B179" s="1">
+        <v>2.52756872312878</v>
+      </c>
+      <c r="C179" s="1">
+        <v>3.98908146812504E-2</v>
+      </c>
+    </row>
+    <row r="180" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A180" s="1" t="s">
+        <v>479</v>
+      </c>
+      <c r="B180" s="1">
+        <v>2.51132793852284</v>
+      </c>
+      <c r="C180" s="1">
+        <v>4.0524916971605499E-2</v>
+      </c>
+    </row>
+    <row r="181" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A181" s="1" t="s">
+        <v>480</v>
+      </c>
+      <c r="B181" s="1">
+        <v>2.5199495004271499</v>
+      </c>
+      <c r="C181" s="1">
+        <v>4.0390455654384101E-2</v>
+      </c>
+    </row>
+    <row r="182" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A182" s="1" t="s">
+        <v>481</v>
+      </c>
+      <c r="B182" s="1">
+        <v>2.5099318931845498</v>
+      </c>
+      <c r="C182" s="1">
+        <v>4.1071400769317298E-2</v>
+      </c>
+    </row>
+    <row r="183" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A183" s="1" t="s">
+        <v>482</v>
+      </c>
+      <c r="B183" s="1">
+        <v>2.5170794909418999</v>
+      </c>
+      <c r="C183" s="1">
+        <v>4.0178381373720602E-2</v>
+      </c>
+    </row>
+    <row r="184" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A184" s="1" t="s">
+        <v>483</v>
+      </c>
+      <c r="B184" s="1">
+        <v>2.5205441270179501</v>
+      </c>
+      <c r="C184" s="1">
+        <v>4.0702941996408802E-2</v>
+      </c>
+    </row>
+    <row r="185" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A185" s="1" t="s">
+        <v>484</v>
+      </c>
+      <c r="B185" s="1">
+        <v>2.5256694865405498</v>
+      </c>
+      <c r="C185" s="1">
+        <v>4.01385052767382E-2</v>
+      </c>
+    </row>
+    <row r="186" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A186" s="1" t="s">
+        <v>485</v>
+      </c>
+      <c r="B186" s="1">
+        <v>2.5268785167168302</v>
+      </c>
+      <c r="C186" s="1">
+        <v>4.0018008651341898E-2</v>
+      </c>
+    </row>
+    <row r="187" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A187" s="1" t="s">
+        <v>486</v>
+      </c>
+      <c r="B187" s="1">
+        <v>2.5179187778053098</v>
+      </c>
+      <c r="C187" s="1">
+        <v>3.9989666024372497E-2</v>
+      </c>
+    </row>
+    <row r="188" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A188" s="1" t="s">
+        <v>487</v>
+      </c>
+      <c r="B188" s="1">
+        <v>2.5003481091105</v>
+      </c>
+      <c r="C188" s="1">
+        <v>4.0322645046764097E-2</v>
+      </c>
+    </row>
+    <row r="189" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A189" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="B189" s="1">
+        <v>2.5011416069930501</v>
+      </c>
+      <c r="C189" s="1">
+        <v>4.0532664600090897E-2</v>
+      </c>
+    </row>
+    <row r="190" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A190" s="1" t="s">
+        <v>489</v>
+      </c>
+      <c r="B190" s="1">
+        <v>2.49799819651472</v>
+      </c>
+      <c r="C190" s="1">
+        <v>4.06963104125408E-2</v>
+      </c>
+    </row>
+    <row r="191" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A191" s="1" t="s">
+        <v>490</v>
+      </c>
+      <c r="B191" s="1">
+        <v>2.5008140111194899</v>
+      </c>
+      <c r="C191" s="1">
+        <v>4.1172181601451197E-2</v>
+      </c>
+    </row>
+    <row r="192" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A192" s="1" t="s">
+        <v>491</v>
+      </c>
+      <c r="B192" s="1">
+        <v>2.4996354690281701</v>
+      </c>
+      <c r="C192" s="1">
+        <v>3.9836921294789503E-2</v>
+      </c>
+    </row>
+    <row r="193" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A193" s="1" t="s">
+        <v>492</v>
+      </c>
+      <c r="B193" s="1">
+        <v>2.4937831454353199</v>
+      </c>
+      <c r="C193" s="1">
+        <v>4.0347554180400501E-2</v>
       </c>
     </row>
   </sheetData>
